--- a/data/H131_20260624_14.xlsx
+++ b/data/H131_20260624_14.xlsx
@@ -451,7 +451,7 @@
         <v>1092.0</v>
       </c>
       <c r="J2" s="2">
-        <v>1023.0</v>
+        <v>1053.0</v>
       </c>
       <c r="K2" s="2">
         <v>1.0</v>
@@ -463,25 +463,25 @@
         <v>0.0</v>
       </c>
       <c r="N2" s="2">
-        <v>1023.0</v>
+        <v>1053.0</v>
       </c>
       <c r="O2" s="2">
-        <v>577.0</v>
+        <v>606.0</v>
       </c>
       <c r="P2" s="2">
         <v>444.0</v>
       </c>
       <c r="Q2" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R2" s="2">
         <v>13.0</v>
       </c>
       <c r="S2" s="2">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="T2" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="U2" s="2">
         <v>0.0</v>
@@ -593,7 +593,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>892.0</v>
+        <v>998.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -605,25 +605,25 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>892.0</v>
+        <v>998.0</v>
       </c>
       <c r="O4" s="2">
-        <v>525.0</v>
+        <v>599.0</v>
       </c>
       <c r="P4" s="2">
-        <v>367.0</v>
+        <v>399.0</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0</v>
       </c>
       <c r="R4" s="2">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="S4" s="2">
         <v>3.0</v>
       </c>
       <c r="T4" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U4" s="2">
         <v>0.0</v>
@@ -632,7 +632,7 @@
         <v>0.0</v>
       </c>
       <c r="W4" s="2">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>631.0</v>
+        <v>632.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -676,7 +676,7 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>631.0</v>
+        <v>632.0</v>
       </c>
       <c r="O5" s="2">
         <v>333.0</v>
@@ -685,7 +685,7 @@
         <v>296.0</v>
       </c>
       <c r="Q5" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R5" s="2">
         <v>24.0</v>
@@ -735,7 +735,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>859.0</v>
+        <v>866.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -747,34 +747,34 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>859.0</v>
+        <v>866.0</v>
       </c>
       <c r="O6" s="2">
         <v>461.0</v>
       </c>
       <c r="P6" s="2">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
       <c r="Q6" s="2">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="R6" s="2">
         <v>37.0</v>
       </c>
       <c r="S6" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="T6" s="2">
         <v>3.0</v>
       </c>
       <c r="U6" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V6" s="2">
         <v>0.0</v>
       </c>
       <c r="W6" s="2">
-        <v>58.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="7">
@@ -806,7 +806,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" s="2">
-        <v>471.0</v>
+        <v>473.0</v>
       </c>
       <c r="K7" s="2">
         <v>1.0</v>
@@ -818,19 +818,19 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <v>471.0</v>
+        <v>473.0</v>
       </c>
       <c r="O7" s="2">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="P7" s="2">
         <v>196.0</v>
       </c>
       <c r="Q7" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R7" s="2">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="S7" s="2">
         <v>13.0</v>
@@ -839,7 +839,7 @@
         <v>4.0</v>
       </c>
       <c r="U7" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="V7" s="2">
         <v>0.0</v>
@@ -877,7 +877,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>633.0</v>
+        <v>659.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -889,16 +889,16 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>633.0</v>
+        <v>659.0</v>
       </c>
       <c r="O8" s="2">
-        <v>375.0</v>
+        <v>385.0</v>
       </c>
       <c r="P8" s="2">
         <v>257.0</v>
       </c>
       <c r="Q8" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="R8" s="2">
         <v>27.0</v>
@@ -948,7 +948,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" s="2">
-        <v>660.0</v>
+        <v>672.0</v>
       </c>
       <c r="K9" s="2">
         <v>1.0</v>
@@ -960,16 +960,16 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="2">
-        <v>660.0</v>
+        <v>672.0</v>
       </c>
       <c r="O9" s="2">
-        <v>368.0</v>
+        <v>373.0</v>
       </c>
       <c r="P9" s="2">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="R9" s="2">
         <v>45.0</v>
@@ -978,7 +978,7 @@
         <v>12.0</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U9" s="2">
         <v>0.0</v>
@@ -987,7 +987,7 @@
         <v>0.0</v>
       </c>
       <c r="W9" s="2">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="10">
@@ -1019,7 +1019,7 @@
         <v>311.0</v>
       </c>
       <c r="J10" s="2">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="K10" s="2">
         <v>1.0</v>
@@ -1031,13 +1031,13 @@
         <v>0.0</v>
       </c>
       <c r="N10" s="2">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="O10" s="2">
         <v>111.0</v>
       </c>
       <c r="P10" s="2">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="Q10" s="2">
         <v>2.0</v>
@@ -1046,7 +1046,7 @@
         <v>9.0</v>
       </c>
       <c r="S10" s="2">
-        <v>49.0</v>
+        <v>53.0</v>
       </c>
       <c r="T10" s="2">
         <v>0.0</v>
@@ -1058,7 +1058,7 @@
         <v>0.0</v>
       </c>
       <c r="W10" s="2">
-        <v>62.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="11">
@@ -1090,7 +1090,7 @@
         <v>561.0</v>
       </c>
       <c r="J11" s="2">
-        <v>554.0</v>
+        <v>561.0</v>
       </c>
       <c r="K11" s="2">
         <v>1.0</v>
@@ -1102,16 +1102,16 @@
         <v>0.0</v>
       </c>
       <c r="N11" s="2">
-        <v>554.0</v>
+        <v>561.0</v>
       </c>
       <c r="O11" s="2">
-        <v>357.0</v>
+        <v>360.0</v>
       </c>
       <c r="P11" s="2">
-        <v>197.0</v>
+        <v>196.0</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R11" s="2">
         <v>0.0</v>
@@ -1161,7 +1161,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" s="2">
-        <v>768.0</v>
+        <v>776.0</v>
       </c>
       <c r="K12" s="2">
         <v>1.0</v>
@@ -1173,19 +1173,19 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <v>768.0</v>
+        <v>776.0</v>
       </c>
       <c r="O12" s="2">
-        <v>439.0</v>
+        <v>443.0</v>
       </c>
       <c r="P12" s="2">
-        <v>324.0</v>
+        <v>326.0</v>
       </c>
       <c r="Q12" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R12" s="2">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="S12" s="2">
         <v>8.0</v>
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="W12" s="2">
-        <v>15.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="13">
@@ -1232,7 +1232,7 @@
         <v>1245.0</v>
       </c>
       <c r="J13" s="2">
-        <v>1201.0</v>
+        <v>1202.0</v>
       </c>
       <c r="K13" s="2">
         <v>1.0</v>
@@ -1244,13 +1244,13 @@
         <v>0.0</v>
       </c>
       <c r="N13" s="2">
-        <v>1201.0</v>
+        <v>1202.0</v>
       </c>
       <c r="O13" s="2">
         <v>649.0</v>
       </c>
       <c r="P13" s="2">
-        <v>552.0</v>
+        <v>553.0</v>
       </c>
       <c r="Q13" s="2">
         <v>0.0</v>
@@ -1259,19 +1259,19 @@
         <v>8.0</v>
       </c>
       <c r="S13" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="T13" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="U13" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V13" s="2">
         <v>0.0</v>
       </c>
       <c r="W13" s="2">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="14">
@@ -1303,7 +1303,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>1242.0</v>
+        <v>1262.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1315,34 +1315,34 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>1242.0</v>
+        <v>1262.0</v>
       </c>
       <c r="O14" s="2">
-        <v>698.0</v>
+        <v>704.0</v>
       </c>
       <c r="P14" s="2">
-        <v>541.0</v>
+        <v>548.0</v>
       </c>
       <c r="Q14" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="R14" s="2">
         <v>37.0</v>
       </c>
       <c r="S14" s="2">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
       <c r="T14" s="2">
         <v>4.0</v>
       </c>
       <c r="U14" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="V14" s="2">
         <v>0.0</v>
       </c>
       <c r="W14" s="2">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="15">
@@ -1374,7 +1374,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>734.0</v>
+        <v>741.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1386,16 +1386,16 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>734.0</v>
+        <v>741.0</v>
       </c>
       <c r="O15" s="2">
         <v>361.0</v>
       </c>
       <c r="P15" s="2">
-        <v>360.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q15" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="R15" s="2">
         <v>22.0</v>
@@ -1404,10 +1404,10 @@
         <v>12.0</v>
       </c>
       <c r="T15" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U15" s="2">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="V15" s="2">
         <v>0.0</v>
@@ -1445,7 +1445,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" s="2">
-        <v>582.0</v>
+        <v>595.0</v>
       </c>
       <c r="K16" s="2">
         <v>1.0</v>
@@ -1457,34 +1457,34 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <v>582.0</v>
+        <v>595.0</v>
       </c>
       <c r="O16" s="2">
-        <v>286.0</v>
+        <v>291.0</v>
       </c>
       <c r="P16" s="2">
-        <v>296.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q16" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="R16" s="2">
         <v>30.0</v>
       </c>
       <c r="S16" s="2">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
       <c r="T16" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U16" s="2">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="V16" s="2">
         <v>0.0</v>
       </c>
       <c r="W16" s="2">
-        <v>101.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="17">
@@ -1516,7 +1516,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>756.0</v>
+        <v>761.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1528,22 +1528,22 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>756.0</v>
+        <v>761.0</v>
       </c>
       <c r="O17" s="2">
         <v>418.0</v>
       </c>
       <c r="P17" s="2">
-        <v>336.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q17" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="R17" s="2">
         <v>30.0</v>
       </c>
       <c r="S17" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="T17" s="2">
         <v>9.0</v>
@@ -1555,7 +1555,7 @@
         <v>0.0</v>
       </c>
       <c r="W17" s="2">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="18">
@@ -1587,7 +1587,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" s="2">
-        <v>1134.0</v>
+        <v>1135.0</v>
       </c>
       <c r="K18" s="2">
         <v>1.0</v>
@@ -1599,7 +1599,7 @@
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <v>1134.0</v>
+        <v>1135.0</v>
       </c>
       <c r="O18" s="2">
         <v>605.0</v>
@@ -1608,7 +1608,7 @@
         <v>529.0</v>
       </c>
       <c r="Q18" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R18" s="2">
         <v>25.0</v>
@@ -1658,7 +1658,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>852.0</v>
+        <v>867.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1670,25 +1670,25 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>852.0</v>
+        <v>867.0</v>
       </c>
       <c r="O19" s="2">
-        <v>459.0</v>
+        <v>468.0</v>
       </c>
       <c r="P19" s="2">
-        <v>391.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q19" s="2">
         <v>2.0</v>
       </c>
       <c r="R19" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="S19" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="T19" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="U19" s="2">
         <v>1.0</v>
@@ -1697,7 +1697,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="20">
@@ -1729,7 +1729,7 @@
         <v>1258.0</v>
       </c>
       <c r="J20" s="2">
-        <v>1180.0</v>
+        <v>1189.0</v>
       </c>
       <c r="K20" s="2">
         <v>1.0</v>
@@ -1738,19 +1738,19 @@
         <v>1.0</v>
       </c>
       <c r="M20" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="2">
-        <v>1179.0</v>
+        <v>1189.0</v>
       </c>
       <c r="O20" s="2">
-        <v>663.0</v>
+        <v>666.0</v>
       </c>
       <c r="P20" s="2">
-        <v>504.0</v>
+        <v>505.0</v>
       </c>
       <c r="Q20" s="2">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="R20" s="2">
         <v>24.0</v>
@@ -1800,7 +1800,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" s="2">
-        <v>756.0</v>
+        <v>762.0</v>
       </c>
       <c r="K21" s="2">
         <v>1.0</v>
@@ -1812,19 +1812,19 @@
         <v>0.0</v>
       </c>
       <c r="N21" s="2">
-        <v>756.0</v>
+        <v>762.0</v>
       </c>
       <c r="O21" s="2">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="P21" s="2">
-        <v>361.0</v>
+        <v>362.0</v>
       </c>
       <c r="Q21" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="R21" s="2">
-        <v>38.0</v>
+        <v>34.0</v>
       </c>
       <c r="S21" s="2">
         <v>32.0</v>
@@ -1839,7 +1839,7 @@
         <v>0.0</v>
       </c>
       <c r="W21" s="2">
-        <v>168.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1871,7 +1871,7 @@
         <v>1003.0</v>
       </c>
       <c r="J22" s="2">
-        <v>894.0</v>
+        <v>898.0</v>
       </c>
       <c r="K22" s="2">
         <v>1.0</v>
@@ -1883,16 +1883,16 @@
         <v>0.0</v>
       </c>
       <c r="N22" s="2">
-        <v>894.0</v>
+        <v>898.0</v>
       </c>
       <c r="O22" s="2">
         <v>504.0</v>
       </c>
       <c r="P22" s="2">
-        <v>390.0</v>
+        <v>389.0</v>
       </c>
       <c r="Q22" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R22" s="2">
         <v>41.0</v>
@@ -1942,7 +1942,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" s="2">
-        <v>716.0</v>
+        <v>734.0</v>
       </c>
       <c r="K23" s="2">
         <v>1.0</v>
@@ -1954,16 +1954,16 @@
         <v>0.0</v>
       </c>
       <c r="N23" s="2">
-        <v>716.0</v>
+        <v>734.0</v>
       </c>
       <c r="O23" s="2">
-        <v>390.0</v>
+        <v>397.0</v>
       </c>
       <c r="P23" s="2">
-        <v>326.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q23" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="R23" s="2">
         <v>3.0</v>
@@ -1975,13 +1975,13 @@
         <v>2.0</v>
       </c>
       <c r="U23" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V23" s="2">
         <v>0.0</v>
       </c>
       <c r="W23" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -2013,7 +2013,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>1215.0</v>
+        <v>1248.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2025,22 +2025,22 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>1215.0</v>
+        <v>1248.0</v>
       </c>
       <c r="O24" s="2">
-        <v>741.0</v>
+        <v>755.0</v>
       </c>
       <c r="P24" s="2">
-        <v>452.0</v>
+        <v>465.0</v>
       </c>
       <c r="Q24" s="2">
-        <v>22.0</v>
+        <v>28.0</v>
       </c>
       <c r="R24" s="2">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="S24" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="T24" s="2">
         <v>6.0</v>
@@ -2052,7 +2052,7 @@
         <v>0.0</v>
       </c>
       <c r="W24" s="2">
-        <v>44.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2084,7 +2084,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" s="2">
-        <v>368.0</v>
+        <v>367.0</v>
       </c>
       <c r="K25" s="2">
         <v>1.0</v>
@@ -2096,10 +2096,10 @@
         <v>0.0</v>
       </c>
       <c r="N25" s="2">
-        <v>368.0</v>
+        <v>367.0</v>
       </c>
       <c r="O25" s="2">
-        <v>263.0</v>
+        <v>262.0</v>
       </c>
       <c r="P25" s="2">
         <v>105.0</v>
@@ -2111,7 +2111,7 @@
         <v>1.0</v>
       </c>
       <c r="S25" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T25" s="2">
         <v>0.0</v>
@@ -2123,7 +2123,7 @@
         <v>0.0</v>
       </c>
       <c r="W25" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2155,7 +2155,7 @@
         <v>1399.0</v>
       </c>
       <c r="J26" s="2">
-        <v>1298.0</v>
+        <v>1301.0</v>
       </c>
       <c r="K26" s="2">
         <v>1.0</v>
@@ -2167,10 +2167,10 @@
         <v>0.0</v>
       </c>
       <c r="N26" s="2">
-        <v>1298.0</v>
+        <v>1301.0</v>
       </c>
       <c r="O26" s="2">
-        <v>677.0</v>
+        <v>680.0</v>
       </c>
       <c r="P26" s="2">
         <v>559.0</v>
@@ -2223,10 +2223,10 @@
         <v>851.0</v>
       </c>
       <c r="I27" s="2">
-        <v>820.0</v>
+        <v>828.0</v>
       </c>
       <c r="J27" s="2">
-        <v>793.0</v>
+        <v>801.0</v>
       </c>
       <c r="K27" s="2">
         <v>1.0</v>
@@ -2238,13 +2238,13 @@
         <v>0.0</v>
       </c>
       <c r="N27" s="2">
-        <v>793.0</v>
+        <v>801.0</v>
       </c>
       <c r="O27" s="2">
-        <v>446.0</v>
+        <v>453.0</v>
       </c>
       <c r="P27" s="2">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
       <c r="Q27" s="2">
         <v>7.0</v>
@@ -2259,13 +2259,13 @@
         <v>3.0</v>
       </c>
       <c r="U27" s="2">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="V27" s="2">
         <v>0.0</v>
       </c>
       <c r="W27" s="2">
-        <v>58.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2297,7 +2297,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>1164.0</v>
+        <v>1223.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2309,34 +2309,34 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>1164.0</v>
+        <v>1223.0</v>
       </c>
       <c r="O28" s="2">
-        <v>660.0</v>
+        <v>706.0</v>
       </c>
       <c r="P28" s="2">
-        <v>502.0</v>
+        <v>515.0</v>
       </c>
       <c r="Q28" s="2">
         <v>2.0</v>
       </c>
       <c r="R28" s="2">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
       <c r="S28" s="2">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
       <c r="T28" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="U28" s="2">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="V28" s="2">
         <v>1.0</v>
       </c>
       <c r="W28" s="2">
-        <v>88.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -2368,7 +2368,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>938.0</v>
+        <v>1024.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2380,34 +2380,34 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>938.0</v>
+        <v>1024.0</v>
       </c>
       <c r="O29" s="2">
-        <v>333.0</v>
+        <v>387.0</v>
       </c>
       <c r="P29" s="2">
-        <v>414.0</v>
+        <v>422.0</v>
       </c>
       <c r="Q29" s="2">
-        <v>191.0</v>
+        <v>215.0</v>
       </c>
       <c r="R29" s="2">
-        <v>5.0</v>
+        <v>47.0</v>
       </c>
       <c r="S29" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="T29" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="U29" s="2">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="V29" s="2">
         <v>0.0</v>
       </c>
       <c r="W29" s="2">
-        <v>5.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -2439,7 +2439,7 @@
         <v>258.0</v>
       </c>
       <c r="J30" s="2">
-        <v>251.0</v>
+        <v>256.0</v>
       </c>
       <c r="K30" s="2">
         <v>1.0</v>
@@ -2448,19 +2448,19 @@
         <v>1.0</v>
       </c>
       <c r="M30" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N30" s="2">
-        <v>251.0</v>
+        <v>255.0</v>
       </c>
       <c r="O30" s="2">
-        <v>143.0</v>
+        <v>163.0</v>
       </c>
       <c r="P30" s="2">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="Q30" s="2">
-        <v>21.0</v>
+        <v>4.0</v>
       </c>
       <c r="R30" s="2">
         <v>3.0</v>
@@ -2581,7 +2581,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" s="2">
-        <v>1021.0</v>
+        <v>1097.0</v>
       </c>
       <c r="K32" s="2">
         <v>1.0</v>
@@ -2593,34 +2593,34 @@
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <v>1021.0</v>
+        <v>1097.0</v>
       </c>
       <c r="O32" s="2">
-        <v>503.0</v>
+        <v>536.0</v>
       </c>
       <c r="P32" s="2">
-        <v>484.0</v>
+        <v>515.0</v>
       </c>
       <c r="Q32" s="2">
-        <v>34.0</v>
+        <v>46.0</v>
       </c>
       <c r="R32" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="S32" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="T32" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U32" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="V32" s="2">
         <v>0.0</v>
       </c>
       <c r="W32" s="2">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -2865,7 +2865,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>969.0</v>
+        <v>1010.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2877,16 +2877,16 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>969.0</v>
+        <v>1010.0</v>
       </c>
       <c r="O36" s="2">
-        <v>481.0</v>
+        <v>492.0</v>
       </c>
       <c r="P36" s="2">
-        <v>466.0</v>
+        <v>479.0</v>
       </c>
       <c r="Q36" s="2">
-        <v>22.0</v>
+        <v>39.0</v>
       </c>
       <c r="R36" s="2">
         <v>45.0</v>
@@ -2895,16 +2895,16 @@
         <v>24.0</v>
       </c>
       <c r="T36" s="2">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="U36" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="V36" s="2">
         <v>0.0</v>
       </c>
       <c r="W36" s="2">
-        <v>87.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -2936,7 +2936,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2948,7 +2948,7 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="O37" s="2">
         <v>256.0</v>
@@ -2957,7 +2957,7 @@
         <v>230.0</v>
       </c>
       <c r="Q37" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R37" s="2">
         <v>25.0</v>
@@ -3007,7 +3007,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" s="2">
-        <v>1050.0</v>
+        <v>1067.0</v>
       </c>
       <c r="K38" s="2">
         <v>1.0</v>
@@ -3019,16 +3019,16 @@
         <v>0.0</v>
       </c>
       <c r="N38" s="2">
-        <v>1050.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O38" s="2">
-        <v>602.0</v>
+        <v>610.0</v>
       </c>
       <c r="P38" s="2">
-        <v>428.0</v>
+        <v>435.0</v>
       </c>
       <c r="Q38" s="2">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="R38" s="2">
         <v>37.0</v>
@@ -3037,16 +3037,16 @@
         <v>9.0</v>
       </c>
       <c r="T38" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U38" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="V38" s="2">
         <v>0.0</v>
       </c>
       <c r="W38" s="2">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -3220,7 +3220,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>1175.0</v>
+        <v>1210.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3232,22 +3232,22 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>1175.0</v>
+        <v>1210.0</v>
       </c>
       <c r="O41" s="2">
-        <v>634.0</v>
+        <v>649.0</v>
       </c>
       <c r="P41" s="2">
-        <v>541.0</v>
+        <v>554.0</v>
       </c>
       <c r="Q41" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="R41" s="2">
         <v>17.0</v>
       </c>
       <c r="S41" s="2">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="T41" s="2">
         <v>2.0</v>
@@ -3259,7 +3259,7 @@
         <v>0.0</v>
       </c>
       <c r="W41" s="2">
-        <v>36.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -3291,7 +3291,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>875.0</v>
+        <v>927.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3303,34 +3303,34 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>875.0</v>
+        <v>927.0</v>
       </c>
       <c r="O42" s="2">
-        <v>554.0</v>
+        <v>586.0</v>
       </c>
       <c r="P42" s="2">
-        <v>319.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q42" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="R42" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>33.0</v>
+      </c>
+      <c r="T42" s="2">
         <v>2.0</v>
       </c>
-      <c r="R42" s="2">
-        <v>34.0</v>
-      </c>
-      <c r="S42" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="T42" s="2">
-        <v>1.0</v>
-      </c>
       <c r="U42" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V42" s="2">
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>42.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3362,7 +3362,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" s="2">
-        <v>969.0</v>
+        <v>982.0</v>
       </c>
       <c r="K43" s="2">
         <v>1.0</v>
@@ -3374,34 +3374,34 @@
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <v>969.0</v>
+        <v>982.0</v>
       </c>
       <c r="O43" s="2">
-        <v>504.0</v>
+        <v>510.0</v>
       </c>
       <c r="P43" s="2">
-        <v>452.0</v>
+        <v>454.0</v>
       </c>
       <c r="Q43" s="2">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="R43" s="2">
         <v>30.0</v>
       </c>
       <c r="S43" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="T43" s="2">
         <v>2.0</v>
       </c>
       <c r="U43" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V43" s="2">
         <v>0.0</v>
       </c>
       <c r="W43" s="2">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -3504,7 +3504,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1102.0</v>
+        <v>1100.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3516,22 +3516,22 @@
         <v>0.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1101.0</v>
+        <v>1100.0</v>
       </c>
       <c r="O45" s="2">
-        <v>518.0</v>
+        <v>519.0</v>
       </c>
       <c r="P45" s="2">
-        <v>545.0</v>
+        <v>544.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>39.0</v>
+        <v>37.0</v>
       </c>
       <c r="R45" s="2">
-        <v>52.0</v>
+        <v>51.0</v>
       </c>
       <c r="S45" s="2">
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
       <c r="T45" s="2">
         <v>5.0</v>
@@ -3543,7 +3543,7 @@
         <v>0.0</v>
       </c>
       <c r="W45" s="2">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3590,13 +3590,13 @@
         <v>1376.0</v>
       </c>
       <c r="O46" s="2">
-        <v>707.0</v>
+        <v>708.0</v>
       </c>
       <c r="P46" s="2">
         <v>611.0</v>
       </c>
       <c r="Q46" s="2">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
       <c r="R46" s="2">
         <v>15.0</v>
@@ -3661,13 +3661,13 @@
         <v>759.0</v>
       </c>
       <c r="O47" s="2">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
       <c r="P47" s="2">
         <v>336.0</v>
       </c>
       <c r="Q47" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="R47" s="2">
         <v>23.0</v>
@@ -3717,7 +3717,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>1040.0</v>
+        <v>1048.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3729,22 +3729,22 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>1040.0</v>
+        <v>1048.0</v>
       </c>
       <c r="O48" s="2">
-        <v>625.0</v>
+        <v>628.0</v>
       </c>
       <c r="P48" s="2">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="Q48" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="R48" s="2">
         <v>30.0</v>
       </c>
       <c r="S48" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T48" s="2">
         <v>5.0</v>
@@ -3756,7 +3756,7 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="2">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -3803,13 +3803,13 @@
         <v>1354.0</v>
       </c>
       <c r="O49" s="2">
-        <v>778.0</v>
+        <v>802.0</v>
       </c>
       <c r="P49" s="2">
         <v>538.0</v>
       </c>
       <c r="Q49" s="2">
-        <v>38.0</v>
+        <v>14.0</v>
       </c>
       <c r="R49" s="2">
         <v>68.0</v>
@@ -3871,7 +3871,7 @@
         <v>3.0</v>
       </c>
       <c r="N50" s="2">
-        <v>555.0</v>
+        <v>554.0</v>
       </c>
       <c r="O50" s="2">
         <v>268.0</v>
@@ -3886,13 +3886,13 @@
         <v>13.0</v>
       </c>
       <c r="S50" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T50" s="2">
         <v>0.0</v>
       </c>
       <c r="U50" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="V50" s="2">
         <v>0.0</v>
@@ -4143,7 +4143,7 @@
         <v>778.0</v>
       </c>
       <c r="J54" s="2">
-        <v>640.0</v>
+        <v>642.0</v>
       </c>
       <c r="K54" s="2">
         <v>1.0</v>
@@ -4155,10 +4155,10 @@
         <v>0.0</v>
       </c>
       <c r="N54" s="2">
-        <v>640.0</v>
+        <v>642.0</v>
       </c>
       <c r="O54" s="2">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
       <c r="P54" s="2">
         <v>302.0</v>
@@ -4170,7 +4170,7 @@
         <v>16.0</v>
       </c>
       <c r="S54" s="2">
-        <v>111.0</v>
+        <v>109.0</v>
       </c>
       <c r="T54" s="2">
         <v>11.0</v>
@@ -4182,7 +4182,7 @@
         <v>0.0</v>
       </c>
       <c r="W54" s="2">
-        <v>138.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
@@ -4285,7 +4285,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>597.0</v>
+        <v>608.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4297,10 +4297,10 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>597.0</v>
+        <v>608.0</v>
       </c>
       <c r="O56" s="2">
-        <v>304.0</v>
+        <v>315.0</v>
       </c>
       <c r="P56" s="2">
         <v>293.0</v>
@@ -4318,13 +4318,13 @@
         <v>0.0</v>
       </c>
       <c r="U56" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="V56" s="2">
         <v>0.0</v>
       </c>
       <c r="W56" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -4427,7 +4427,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" s="2">
-        <v>1043.0</v>
+        <v>1046.0</v>
       </c>
       <c r="K58" s="2">
         <v>1.0</v>
@@ -4439,16 +4439,16 @@
         <v>0.0</v>
       </c>
       <c r="N58" s="2">
-        <v>1043.0</v>
+        <v>1046.0</v>
       </c>
       <c r="O58" s="2">
-        <v>565.0</v>
+        <v>567.0</v>
       </c>
       <c r="P58" s="2">
         <v>476.0</v>
       </c>
       <c r="Q58" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R58" s="2">
         <v>10.0</v>
@@ -4498,7 +4498,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>845.0</v>
+        <v>846.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4510,7 +4510,7 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>845.0</v>
+        <v>846.0</v>
       </c>
       <c r="O59" s="2">
         <v>426.0</v>
@@ -4519,7 +4519,7 @@
         <v>415.0</v>
       </c>
       <c r="Q59" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R59" s="2">
         <v>35.0</v>
@@ -4569,7 +4569,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" s="2">
-        <v>662.0</v>
+        <v>664.0</v>
       </c>
       <c r="K60" s="2">
         <v>1.0</v>
@@ -4581,7 +4581,7 @@
         <v>0.0</v>
       </c>
       <c r="N60" s="2">
-        <v>662.0</v>
+        <v>664.0</v>
       </c>
       <c r="O60" s="2">
         <v>296.0</v>
@@ -4590,13 +4590,13 @@
         <v>364.0</v>
       </c>
       <c r="Q60" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R60" s="2">
         <v>12.0</v>
       </c>
       <c r="S60" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T60" s="2">
         <v>4.0</v>
@@ -4608,7 +4608,7 @@
         <v>0.0</v>
       </c>
       <c r="W60" s="2">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -4640,7 +4640,7 @@
         <v>1079.0</v>
       </c>
       <c r="J61" s="2">
-        <v>963.0</v>
+        <v>971.0</v>
       </c>
       <c r="K61" s="2">
         <v>1.0</v>
@@ -4652,16 +4652,16 @@
         <v>0.0</v>
       </c>
       <c r="N61" s="2">
-        <v>963.0</v>
+        <v>971.0</v>
       </c>
       <c r="O61" s="2">
-        <v>481.0</v>
+        <v>485.0</v>
       </c>
       <c r="P61" s="2">
-        <v>465.0</v>
+        <v>466.0</v>
       </c>
       <c r="Q61" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="R61" s="2">
         <v>45.0</v>
@@ -4670,16 +4670,16 @@
         <v>49.0</v>
       </c>
       <c r="T61" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U61" s="2">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="V61" s="2">
         <v>0.0</v>
       </c>
       <c r="W61" s="2">
-        <v>101.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
@@ -4711,7 +4711,7 @@
         <v>570.0</v>
       </c>
       <c r="J62" s="2">
-        <v>517.0</v>
+        <v>518.0</v>
       </c>
       <c r="K62" s="2">
         <v>1.0</v>
@@ -4723,10 +4723,10 @@
         <v>0.0</v>
       </c>
       <c r="N62" s="2">
-        <v>517.0</v>
+        <v>518.0</v>
       </c>
       <c r="O62" s="2">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="P62" s="2">
         <v>231.0</v>
@@ -4735,7 +4735,7 @@
         <v>1.0</v>
       </c>
       <c r="R62" s="2">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="S62" s="2">
         <v>12.0</v>
@@ -4750,7 +4750,7 @@
         <v>0.0</v>
       </c>
       <c r="W62" s="2">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -4782,7 +4782,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>1056.0</v>
+        <v>1088.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4794,13 +4794,13 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>1056.0</v>
+        <v>1088.0</v>
       </c>
       <c r="O63" s="2">
-        <v>641.0</v>
+        <v>656.0</v>
       </c>
       <c r="P63" s="2">
-        <v>414.0</v>
+        <v>431.0</v>
       </c>
       <c r="Q63" s="2">
         <v>1.0</v>
@@ -4809,19 +4809,19 @@
         <v>47.0</v>
       </c>
       <c r="S63" s="2">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="T63" s="2">
         <v>0.0</v>
       </c>
       <c r="U63" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="V63" s="2">
         <v>0.0</v>
       </c>
       <c r="W63" s="2">
-        <v>57.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -4853,7 +4853,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" s="2">
-        <v>1086.0</v>
+        <v>1089.0</v>
       </c>
       <c r="K64" s="2">
         <v>1.0</v>
@@ -4865,16 +4865,16 @@
         <v>0.0</v>
       </c>
       <c r="N64" s="2">
-        <v>1086.0</v>
+        <v>1089.0</v>
       </c>
       <c r="O64" s="2">
         <v>622.0</v>
       </c>
       <c r="P64" s="2">
-        <v>464.0</v>
+        <v>465.0</v>
       </c>
       <c r="Q64" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R64" s="2">
         <v>10.0</v>
@@ -4883,16 +4883,16 @@
         <v>7.0</v>
       </c>
       <c r="T64" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="U64" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="V64" s="2">
         <v>0.0</v>
       </c>
       <c r="W64" s="2">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
@@ -4924,7 +4924,7 @@
         <v>522.0</v>
       </c>
       <c r="J65" s="2">
-        <v>500.0</v>
+        <v>502.0</v>
       </c>
       <c r="K65" s="2">
         <v>1.0</v>
@@ -4936,13 +4936,13 @@
         <v>0.0</v>
       </c>
       <c r="N65" s="2">
-        <v>500.0</v>
+        <v>502.0</v>
       </c>
       <c r="O65" s="2">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="P65" s="2">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="Q65" s="2">
         <v>0.0</v>
@@ -4957,13 +4957,13 @@
         <v>3.0</v>
       </c>
       <c r="U65" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="V65" s="2">
         <v>0.0</v>
       </c>
       <c r="W65" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
@@ -5010,10 +5010,10 @@
         <v>1065.0</v>
       </c>
       <c r="O66" s="2">
-        <v>576.0</v>
+        <v>579.0</v>
       </c>
       <c r="P66" s="2">
-        <v>482.0</v>
+        <v>479.0</v>
       </c>
       <c r="Q66" s="2">
         <v>7.0</v>
@@ -5066,7 +5066,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" s="2">
-        <v>1048.0</v>
+        <v>1049.0</v>
       </c>
       <c r="K67" s="2">
         <v>1.0</v>
@@ -5078,19 +5078,19 @@
         <v>0.0</v>
       </c>
       <c r="N67" s="2">
-        <v>1048.0</v>
+        <v>1049.0</v>
       </c>
       <c r="O67" s="2">
         <v>501.0</v>
       </c>
       <c r="P67" s="2">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="Q67" s="2">
         <v>36.0</v>
       </c>
       <c r="R67" s="2">
-        <v>61.0</v>
+        <v>60.0</v>
       </c>
       <c r="S67" s="2">
         <v>20.0</v>
@@ -5105,7 +5105,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" s="2">
-        <v>81.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -5137,7 +5137,7 @@
         <v>1042.0</v>
       </c>
       <c r="J68" s="2">
-        <v>991.0</v>
+        <v>993.0</v>
       </c>
       <c r="K68" s="2">
         <v>1.0</v>
@@ -5149,7 +5149,7 @@
         <v>0.0</v>
       </c>
       <c r="N68" s="2">
-        <v>991.0</v>
+        <v>993.0</v>
       </c>
       <c r="O68" s="2">
         <v>532.0</v>
@@ -5158,7 +5158,7 @@
         <v>440.0</v>
       </c>
       <c r="Q68" s="2">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="R68" s="2">
         <v>15.0</v>
@@ -5279,7 +5279,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" s="2">
-        <v>1117.0</v>
+        <v>1120.0</v>
       </c>
       <c r="K70" s="2">
         <v>1.0</v>
@@ -5291,16 +5291,16 @@
         <v>0.0</v>
       </c>
       <c r="N70" s="2">
-        <v>1117.0</v>
+        <v>1120.0</v>
       </c>
       <c r="O70" s="2">
-        <v>695.0</v>
+        <v>697.0</v>
       </c>
       <c r="P70" s="2">
         <v>411.0</v>
       </c>
       <c r="Q70" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R70" s="2">
         <v>12.0</v>
@@ -5312,13 +5312,13 @@
         <v>0.0</v>
       </c>
       <c r="U70" s="2">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="V70" s="2">
         <v>0.0</v>
       </c>
       <c r="W70" s="2">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -5350,7 +5350,7 @@
         <v>1228.0</v>
       </c>
       <c r="J71" s="2">
-        <v>1168.0</v>
+        <v>1165.0</v>
       </c>
       <c r="K71" s="2">
         <v>1.0</v>
@@ -5362,13 +5362,13 @@
         <v>0.0</v>
       </c>
       <c r="N71" s="2">
-        <v>1168.0</v>
+        <v>1165.0</v>
       </c>
       <c r="O71" s="2">
-        <v>623.0</v>
+        <v>622.0</v>
       </c>
       <c r="P71" s="2">
-        <v>539.0</v>
+        <v>537.0</v>
       </c>
       <c r="Q71" s="2">
         <v>6.0</v>
@@ -5380,7 +5380,7 @@
         <v>30.0</v>
       </c>
       <c r="T71" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="U71" s="2">
         <v>1.0</v>
@@ -5389,7 +5389,7 @@
         <v>0.0</v>
       </c>
       <c r="W71" s="2">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
@@ -5436,10 +5436,10 @@
         <v>1067.0</v>
       </c>
       <c r="O72" s="2">
-        <v>663.0</v>
+        <v>664.0</v>
       </c>
       <c r="P72" s="2">
-        <v>396.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q72" s="2">
         <v>8.0</v>
@@ -5492,7 +5492,7 @@
         <v>973.0</v>
       </c>
       <c r="J73" s="2">
-        <v>961.0</v>
+        <v>962.0</v>
       </c>
       <c r="K73" s="2">
         <v>1.0</v>
@@ -5504,13 +5504,13 @@
         <v>0.0</v>
       </c>
       <c r="N73" s="2">
-        <v>961.0</v>
+        <v>962.0</v>
       </c>
       <c r="O73" s="2">
         <v>498.0</v>
       </c>
       <c r="P73" s="2">
-        <v>446.0</v>
+        <v>447.0</v>
       </c>
       <c r="Q73" s="2">
         <v>17.0</v>
@@ -5578,13 +5578,13 @@
         <v>733.0</v>
       </c>
       <c r="O74" s="2">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="P74" s="2">
         <v>320.0</v>
       </c>
       <c r="Q74" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="R74" s="2">
         <v>14.0</v>
@@ -5634,7 +5634,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" s="2">
-        <v>815.0</v>
+        <v>823.0</v>
       </c>
       <c r="K75" s="2">
         <v>1.0</v>
@@ -5646,34 +5646,34 @@
         <v>0.0</v>
       </c>
       <c r="N75" s="2">
-        <v>815.0</v>
+        <v>823.0</v>
       </c>
       <c r="O75" s="2">
-        <v>425.0</v>
+        <v>428.0</v>
       </c>
       <c r="P75" s="2">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="Q75" s="2">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="R75" s="2">
         <v>4.0</v>
       </c>
       <c r="S75" s="2">
-        <v>46.0</v>
+        <v>42.0</v>
       </c>
       <c r="T75" s="2">
         <v>2.0</v>
       </c>
       <c r="U75" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="V75" s="2">
         <v>0.0</v>
       </c>
       <c r="W75" s="2">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
@@ -5705,7 +5705,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" s="2">
-        <v>892.0</v>
+        <v>893.0</v>
       </c>
       <c r="K76" s="2">
         <v>1.0</v>
@@ -5717,19 +5717,19 @@
         <v>0.0</v>
       </c>
       <c r="N76" s="2">
-        <v>892.0</v>
+        <v>893.0</v>
       </c>
       <c r="O76" s="2">
         <v>487.0</v>
       </c>
       <c r="P76" s="2">
-        <v>405.0</v>
+        <v>406.0</v>
       </c>
       <c r="Q76" s="2">
         <v>0.0</v>
       </c>
       <c r="R76" s="2">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="S76" s="2">
         <v>33.0</v>
@@ -5744,7 +5744,7 @@
         <v>0.0</v>
       </c>
       <c r="W76" s="2">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
@@ -5776,7 +5776,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>724.0</v>
+        <v>757.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5788,16 +5788,16 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>724.0</v>
+        <v>757.0</v>
       </c>
       <c r="O77" s="2">
-        <v>207.0</v>
+        <v>214.0</v>
       </c>
       <c r="P77" s="2">
-        <v>353.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q77" s="2">
-        <v>164.0</v>
+        <v>185.0</v>
       </c>
       <c r="R77" s="2">
         <v>34.0</v>
@@ -5847,7 +5847,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>1110.0</v>
+        <v>1121.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5859,34 +5859,34 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>1110.0</v>
+        <v>1121.0</v>
       </c>
       <c r="O78" s="2">
-        <v>510.0</v>
+        <v>516.0</v>
       </c>
       <c r="P78" s="2">
-        <v>600.0</v>
+        <v>603.0</v>
       </c>
       <c r="Q78" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R78" s="2">
         <v>54.0</v>
       </c>
       <c r="S78" s="2">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="T78" s="2">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="U78" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="V78" s="2">
         <v>1.0</v>
       </c>
       <c r="W78" s="2">
-        <v>138.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
@@ -6202,7 +6202,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" s="2">
-        <v>1053.0</v>
+        <v>1054.0</v>
       </c>
       <c r="K83" s="2">
         <v>1.0</v>
@@ -6214,13 +6214,13 @@
         <v>0.0</v>
       </c>
       <c r="N83" s="2">
-        <v>1053.0</v>
+        <v>1054.0</v>
       </c>
       <c r="O83" s="2">
         <v>574.0</v>
       </c>
       <c r="P83" s="2">
-        <v>455.0</v>
+        <v>456.0</v>
       </c>
       <c r="Q83" s="2">
         <v>24.0</v>
@@ -6359,10 +6359,10 @@
         <v>1213.0</v>
       </c>
       <c r="O85" s="2">
-        <v>595.0</v>
+        <v>596.0</v>
       </c>
       <c r="P85" s="2">
-        <v>606.0</v>
+        <v>605.0</v>
       </c>
       <c r="Q85" s="2">
         <v>12.0</v>
@@ -6415,7 +6415,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" s="2">
-        <v>1212.0</v>
+        <v>1217.0</v>
       </c>
       <c r="K86" s="2">
         <v>1.0</v>
@@ -6427,25 +6427,25 @@
         <v>0.0</v>
       </c>
       <c r="N86" s="2">
-        <v>1212.0</v>
+        <v>1217.0</v>
       </c>
       <c r="O86" s="2">
-        <v>682.0</v>
+        <v>684.0</v>
       </c>
       <c r="P86" s="2">
-        <v>529.0</v>
+        <v>531.0</v>
       </c>
       <c r="Q86" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R86" s="2">
         <v>9.0</v>
       </c>
       <c r="S86" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="T86" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U86" s="2">
         <v>5.0</v>
@@ -6454,7 +6454,7 @@
         <v>0.0</v>
       </c>
       <c r="W86" s="2">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
@@ -6557,7 +6557,7 @@
         <v>883.0</v>
       </c>
       <c r="J88" s="2">
-        <v>800.0</v>
+        <v>804.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6569,13 +6569,13 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>800.0</v>
+        <v>804.0</v>
       </c>
       <c r="O88" s="2">
-        <v>403.0</v>
+        <v>406.0</v>
       </c>
       <c r="P88" s="2">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
@@ -6584,7 +6584,7 @@
         <v>40.0</v>
       </c>
       <c r="S88" s="2">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="T88" s="2">
         <v>6.0</v>
@@ -6596,7 +6596,7 @@
         <v>1.0</v>
       </c>
       <c r="W88" s="2">
-        <v>80.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
@@ -6640,7 +6640,7 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>750.0</v>
+        <v>749.0</v>
       </c>
       <c r="O89" s="2">
         <v>422.0</v>
@@ -6699,7 +6699,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" s="2">
-        <v>663.0</v>
+        <v>662.0</v>
       </c>
       <c r="K90" s="2">
         <v>1.0</v>
@@ -6711,13 +6711,13 @@
         <v>0.0</v>
       </c>
       <c r="N90" s="2">
-        <v>663.0</v>
+        <v>662.0</v>
       </c>
       <c r="O90" s="2">
         <v>338.0</v>
       </c>
       <c r="P90" s="2">
-        <v>323.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q90" s="2">
         <v>2.0</v>
@@ -6726,7 +6726,7 @@
         <v>14.0</v>
       </c>
       <c r="S90" s="2">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="T90" s="2">
         <v>2.0</v>
@@ -6738,7 +6738,7 @@
         <v>0.0</v>
       </c>
       <c r="W90" s="2">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
@@ -6770,7 +6770,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>727.0</v>
+        <v>729.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6782,16 +6782,16 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>727.0</v>
+        <v>729.0</v>
       </c>
       <c r="O91" s="2">
-        <v>206.0</v>
+        <v>263.0</v>
       </c>
       <c r="P91" s="2">
-        <v>341.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>180.0</v>
+        <v>118.0</v>
       </c>
       <c r="R91" s="2">
         <v>44.0</v>
@@ -6803,13 +6803,13 @@
         <v>4.0</v>
       </c>
       <c r="U91" s="2">
-        <v>131.0</v>
+        <v>129.0</v>
       </c>
       <c r="V91" s="2">
         <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>213.0</v>
+        <v>211.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6927,13 +6927,13 @@
         <v>858.0</v>
       </c>
       <c r="O93" s="2">
-        <v>495.0</v>
+        <v>496.0</v>
       </c>
       <c r="P93" s="2">
         <v>362.0</v>
       </c>
       <c r="Q93" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="R93" s="2">
         <v>56.0</v>
@@ -7054,7 +7054,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" s="2">
-        <v>1413.0</v>
+        <v>1418.0</v>
       </c>
       <c r="K95" s="2">
         <v>1.0</v>
@@ -7066,13 +7066,13 @@
         <v>0.0</v>
       </c>
       <c r="N95" s="2">
-        <v>1413.0</v>
+        <v>1418.0</v>
       </c>
       <c r="O95" s="2">
-        <v>755.0</v>
+        <v>766.0</v>
       </c>
       <c r="P95" s="2">
-        <v>658.0</v>
+        <v>652.0</v>
       </c>
       <c r="Q95" s="2">
         <v>0.0</v>
@@ -7081,7 +7081,7 @@
         <v>1.0</v>
       </c>
       <c r="S95" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T95" s="2">
         <v>0.0</v>
@@ -7093,7 +7093,7 @@
         <v>0.0</v>
       </c>
       <c r="W95" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
@@ -7125,7 +7125,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>1325.0</v>
+        <v>1332.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7137,19 +7137,19 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>1325.0</v>
+        <v>1332.0</v>
       </c>
       <c r="O96" s="2">
-        <v>792.0</v>
+        <v>794.0</v>
       </c>
       <c r="P96" s="2">
-        <v>516.0</v>
+        <v>521.0</v>
       </c>
       <c r="Q96" s="2">
         <v>17.0</v>
       </c>
       <c r="R96" s="2">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="S96" s="2">
         <v>36.0</v>
@@ -7164,7 +7164,7 @@
         <v>0.0</v>
       </c>
       <c r="W96" s="2">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
@@ -7220,7 +7220,7 @@
         <v>18.0</v>
       </c>
       <c r="R97" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="S97" s="2">
         <v>23.0</v>
@@ -7235,7 +7235,7 @@
         <v>0.0</v>
       </c>
       <c r="W97" s="2">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
@@ -7267,7 +7267,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>1376.0</v>
+        <v>1392.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7279,34 +7279,34 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>1376.0</v>
+        <v>1392.0</v>
       </c>
       <c r="O98" s="2">
-        <v>736.0</v>
+        <v>744.0</v>
       </c>
       <c r="P98" s="2">
-        <v>623.0</v>
+        <v>625.0</v>
       </c>
       <c r="Q98" s="2">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="R98" s="2">
         <v>27.0</v>
       </c>
       <c r="S98" s="2">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
       <c r="T98" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U98" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V98" s="2">
         <v>1.0</v>
       </c>
       <c r="W98" s="2">
-        <v>64.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7338,7 +7338,7 @@
         <v>880.0</v>
       </c>
       <c r="J99" s="2">
-        <v>811.0</v>
+        <v>812.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7350,7 +7350,7 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>811.0</v>
+        <v>812.0</v>
       </c>
       <c r="O99" s="2">
         <v>416.0</v>
@@ -7359,13 +7359,13 @@
         <v>392.0</v>
       </c>
       <c r="Q99" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R99" s="2">
         <v>39.0</v>
       </c>
       <c r="S99" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="T99" s="2">
         <v>10.0</v>
@@ -7377,7 +7377,7 @@
         <v>0.0</v>
       </c>
       <c r="W99" s="2">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
@@ -7409,7 +7409,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>1244.0</v>
+        <v>1245.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7421,16 +7421,16 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>1244.0</v>
+        <v>1245.0</v>
       </c>
       <c r="O100" s="2">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="P100" s="2">
-        <v>635.0</v>
+        <v>634.0</v>
       </c>
       <c r="Q100" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R100" s="2">
         <v>0.0</v>
@@ -7439,16 +7439,16 @@
         <v>4.0</v>
       </c>
       <c r="T100" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U100" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V100" s="2">
         <v>0.0</v>
       </c>
       <c r="W100" s="2">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
@@ -7507,7 +7507,7 @@
         <v>46.0</v>
       </c>
       <c r="S101" s="2">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="T101" s="2">
         <v>3.0</v>
@@ -7519,7 +7519,7 @@
         <v>0.0</v>
       </c>
       <c r="W101" s="2">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
@@ -7551,7 +7551,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>1034.0</v>
+        <v>1035.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7563,10 +7563,10 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>1034.0</v>
+        <v>1035.0</v>
       </c>
       <c r="O102" s="2">
-        <v>551.0</v>
+        <v>552.0</v>
       </c>
       <c r="P102" s="2">
         <v>483.0</v>
@@ -7619,10 +7619,10 @@
         <v>664.0</v>
       </c>
       <c r="I103" s="2">
-        <v>663.0</v>
+        <v>664.0</v>
       </c>
       <c r="J103" s="2">
-        <v>609.0</v>
+        <v>613.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7634,22 +7634,22 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>609.0</v>
+        <v>613.0</v>
       </c>
       <c r="O103" s="2">
-        <v>356.0</v>
+        <v>357.0</v>
       </c>
       <c r="P103" s="2">
-        <v>246.0</v>
+        <v>248.0</v>
       </c>
       <c r="Q103" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R103" s="2">
         <v>24.0</v>
       </c>
       <c r="S103" s="2">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="T103" s="2">
         <v>0.0</v>
@@ -7661,7 +7661,7 @@
         <v>0.0</v>
       </c>
       <c r="W103" s="2">
-        <v>52.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -7764,7 +7764,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>905.0</v>
+        <v>904.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7776,10 +7776,10 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>905.0</v>
+        <v>904.0</v>
       </c>
       <c r="O105" s="2">
-        <v>505.0</v>
+        <v>504.0</v>
       </c>
       <c r="P105" s="2">
         <v>377.0</v>
@@ -7794,7 +7794,7 @@
         <v>121.0</v>
       </c>
       <c r="T105" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U105" s="2">
         <v>0.0</v>
@@ -7803,7 +7803,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" s="2">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -7906,7 +7906,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>950.0</v>
+        <v>959.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7918,13 +7918,13 @@
         <v>0.0</v>
       </c>
       <c r="N107" s="2">
-        <v>950.0</v>
+        <v>959.0</v>
       </c>
       <c r="O107" s="2">
-        <v>499.0</v>
+        <v>504.0</v>
       </c>
       <c r="P107" s="2">
-        <v>451.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
@@ -7933,7 +7933,7 @@
         <v>12.0</v>
       </c>
       <c r="S107" s="2">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="T107" s="2">
         <v>0.0</v>
@@ -7945,7 +7945,7 @@
         <v>0.0</v>
       </c>
       <c r="W107" s="2">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
@@ -7977,7 +7977,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" s="2">
-        <v>895.0</v>
+        <v>897.0</v>
       </c>
       <c r="K108" s="2">
         <v>1.0</v>
@@ -7989,10 +7989,10 @@
         <v>0.0</v>
       </c>
       <c r="N108" s="2">
-        <v>895.0</v>
+        <v>897.0</v>
       </c>
       <c r="O108" s="2">
-        <v>563.0</v>
+        <v>565.0</v>
       </c>
       <c r="P108" s="2">
         <v>332.0</v>
@@ -8048,7 +8048,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" s="2">
-        <v>771.0</v>
+        <v>765.0</v>
       </c>
       <c r="K109" s="2">
         <v>1.0</v>
@@ -8060,25 +8060,25 @@
         <v>0.0</v>
       </c>
       <c r="N109" s="2">
-        <v>771.0</v>
+        <v>765.0</v>
       </c>
       <c r="O109" s="2">
-        <v>418.0</v>
+        <v>417.0</v>
       </c>
       <c r="P109" s="2">
-        <v>341.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q109" s="2">
         <v>12.0</v>
       </c>
       <c r="R109" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="S109" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="T109" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U109" s="2">
         <v>2.0</v>
@@ -8087,7 +8087,7 @@
         <v>0.0</v>
       </c>
       <c r="W109" s="2">
-        <v>50.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
@@ -8403,7 +8403,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>866.0</v>
+        <v>886.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8415,19 +8415,19 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>866.0</v>
+        <v>886.0</v>
       </c>
       <c r="O114" s="2">
-        <v>525.0</v>
+        <v>532.0</v>
       </c>
       <c r="P114" s="2">
-        <v>340.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q114" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="R114" s="2">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="S114" s="2">
         <v>7.0</v>
@@ -8442,7 +8442,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8545,7 +8545,7 @@
         <v>1148.0</v>
       </c>
       <c r="J116" s="2">
-        <v>833.0</v>
+        <v>948.0</v>
       </c>
       <c r="K116" s="2">
         <v>1.0</v>
@@ -8557,25 +8557,25 @@
         <v>1.0</v>
       </c>
       <c r="N116" s="2">
-        <v>832.0</v>
+        <v>947.0</v>
       </c>
       <c r="O116" s="2">
-        <v>76.0</v>
+        <v>136.0</v>
       </c>
       <c r="P116" s="2">
-        <v>360.0</v>
+        <v>415.0</v>
       </c>
       <c r="Q116" s="2">
         <v>397.0</v>
       </c>
       <c r="R116" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="S116" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="T116" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U116" s="2">
         <v>0.0</v>
@@ -8584,7 +8584,7 @@
         <v>0.0</v>
       </c>
       <c r="W116" s="2">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
@@ -8616,7 +8616,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>923.0</v>
+        <v>953.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8628,13 +8628,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>922.0</v>
+        <v>952.0</v>
       </c>
       <c r="O117" s="2">
+        <v>480.0</v>
+      </c>
+      <c r="P117" s="2">
         <v>455.0</v>
-      </c>
-      <c r="P117" s="2">
-        <v>450.0</v>
       </c>
       <c r="Q117" s="2">
         <v>18.0</v>
@@ -8643,7 +8643,7 @@
         <v>27.0</v>
       </c>
       <c r="S117" s="2">
-        <v>82.0</v>
+        <v>86.0</v>
       </c>
       <c r="T117" s="2">
         <v>0.0</v>
@@ -8655,7 +8655,7 @@
         <v>0.0</v>
       </c>
       <c r="W117" s="2">
-        <v>121.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
@@ -8687,7 +8687,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>1152.0</v>
+        <v>1278.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8699,25 +8699,25 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>1152.0</v>
+        <v>1278.0</v>
       </c>
       <c r="O118" s="2">
-        <v>654.0</v>
+        <v>693.0</v>
       </c>
       <c r="P118" s="2">
-        <v>492.0</v>
+        <v>557.0</v>
       </c>
       <c r="Q118" s="2">
-        <v>6.0</v>
+        <v>28.0</v>
       </c>
       <c r="R118" s="2">
-        <v>62.0</v>
+        <v>70.0</v>
       </c>
       <c r="S118" s="2">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="T118" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="U118" s="2">
         <v>28.0</v>
@@ -8726,7 +8726,7 @@
         <v>7.0</v>
       </c>
       <c r="W118" s="2">
-        <v>132.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
@@ -8758,7 +8758,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>980.0</v>
+        <v>983.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8770,19 +8770,19 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>980.0</v>
+        <v>983.0</v>
       </c>
       <c r="O119" s="2">
         <v>565.0</v>
       </c>
       <c r="P119" s="2">
-        <v>393.0</v>
+        <v>396.0</v>
       </c>
       <c r="Q119" s="2">
         <v>22.0</v>
       </c>
       <c r="R119" s="2">
-        <v>72.0</v>
+        <v>71.0</v>
       </c>
       <c r="S119" s="2">
         <v>20.0</v>
@@ -8791,13 +8791,13 @@
         <v>0.0</v>
       </c>
       <c r="U119" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="V119" s="2">
         <v>0.0</v>
       </c>
       <c r="W119" s="2">
-        <v>104.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -8829,7 +8829,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>877.0</v>
+        <v>905.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8841,25 +8841,25 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>877.0</v>
+        <v>905.0</v>
       </c>
       <c r="O120" s="2">
-        <v>484.0</v>
+        <v>502.0</v>
       </c>
       <c r="P120" s="2">
-        <v>358.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q120" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="R120" s="2">
-        <v>47.0</v>
+        <v>52.0</v>
       </c>
       <c r="S120" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="T120" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U120" s="2">
         <v>3.0</v>
@@ -8868,7 +8868,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" s="2">
-        <v>59.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -8900,7 +8900,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>1300.0</v>
+        <v>1372.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8912,22 +8912,22 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>1300.0</v>
+        <v>1372.0</v>
       </c>
       <c r="O121" s="2">
-        <v>819.0</v>
+        <v>843.0</v>
       </c>
       <c r="P121" s="2">
-        <v>455.0</v>
+        <v>492.0</v>
       </c>
       <c r="Q121" s="2">
-        <v>26.0</v>
+        <v>37.0</v>
       </c>
       <c r="R121" s="2">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
       <c r="S121" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="T121" s="2">
         <v>0.0</v>
@@ -8939,7 +8939,7 @@
         <v>0.0</v>
       </c>
       <c r="W121" s="2">
-        <v>48.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -8971,7 +8971,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>783.0</v>
+        <v>856.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8983,34 +8983,34 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>779.0</v>
+        <v>852.0</v>
       </c>
       <c r="O122" s="2">
-        <v>430.0</v>
+        <v>478.0</v>
       </c>
       <c r="P122" s="2">
-        <v>338.0</v>
+        <v>354.0</v>
       </c>
       <c r="Q122" s="2">
-        <v>15.0</v>
+        <v>24.0</v>
       </c>
       <c r="R122" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="S122" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="T122" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U122" s="2">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="V122" s="2">
         <v>2.0</v>
       </c>
       <c r="W122" s="2">
-        <v>73.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
@@ -9486,10 +9486,10 @@
         <v>736.0</v>
       </c>
       <c r="P129" s="2">
-        <v>347.0</v>
+        <v>346.0</v>
       </c>
       <c r="Q129" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="R129" s="2">
         <v>88.0</v>
@@ -9696,16 +9696,16 @@
         <v>1359.0</v>
       </c>
       <c r="O132" s="2">
-        <v>769.0</v>
+        <v>776.0</v>
       </c>
       <c r="P132" s="2">
         <v>567.0</v>
       </c>
       <c r="Q132" s="2">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="R132" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="S132" s="2">
         <v>3.0</v>
@@ -9720,7 +9720,7 @@
         <v>0.0</v>
       </c>
       <c r="W132" s="2">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -9965,7 +9965,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>1043.0</v>
+        <v>1044.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9977,16 +9977,16 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>1043.0</v>
+        <v>1044.0</v>
       </c>
       <c r="O136" s="2">
-        <v>532.0</v>
+        <v>535.0</v>
       </c>
       <c r="P136" s="2">
-        <v>467.0</v>
+        <v>468.0</v>
       </c>
       <c r="Q136" s="2">
-        <v>44.0</v>
+        <v>41.0</v>
       </c>
       <c r="R136" s="2">
         <v>36.0</v>
@@ -10036,7 +10036,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>1002.0</v>
+        <v>1127.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10048,34 +10048,34 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>1002.0</v>
+        <v>1127.0</v>
       </c>
       <c r="O137" s="2">
-        <v>544.0</v>
+        <v>634.0</v>
       </c>
       <c r="P137" s="2">
-        <v>427.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q137" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="R137" s="2">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="S137" s="2">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="T137" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U137" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="V137" s="2">
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>78.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10122,13 +10122,13 @@
         <v>1035.0</v>
       </c>
       <c r="O138" s="2">
-        <v>655.0</v>
+        <v>678.0</v>
       </c>
       <c r="P138" s="2">
-        <v>356.0</v>
+        <v>355.0</v>
       </c>
       <c r="Q138" s="2">
-        <v>24.0</v>
+        <v>2.0</v>
       </c>
       <c r="R138" s="2">
         <v>39.0</v>
@@ -10193,13 +10193,13 @@
         <v>1151.0</v>
       </c>
       <c r="O139" s="2">
-        <v>719.0</v>
+        <v>739.0</v>
       </c>
       <c r="P139" s="2">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
       <c r="Q139" s="2">
-        <v>23.0</v>
+        <v>2.0</v>
       </c>
       <c r="R139" s="2">
         <v>31.0</v>
@@ -10249,7 +10249,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>1118.0</v>
+        <v>1119.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10261,10 +10261,10 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>1118.0</v>
+        <v>1119.0</v>
       </c>
       <c r="O140" s="2">
-        <v>603.0</v>
+        <v>604.0</v>
       </c>
       <c r="P140" s="2">
         <v>491.0</v>
@@ -10320,7 +10320,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>1128.0</v>
+        <v>1173.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10332,34 +10332,34 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>1127.0</v>
+        <v>1172.0</v>
       </c>
       <c r="O141" s="2">
-        <v>696.0</v>
+        <v>721.0</v>
       </c>
       <c r="P141" s="2">
-        <v>416.0</v>
+        <v>431.0</v>
       </c>
       <c r="Q141" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="R141" s="2">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="S141" s="2">
-        <v>12.0</v>
+        <v>26.0</v>
       </c>
       <c r="T141" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="U141" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="V141" s="2">
         <v>1.0</v>
       </c>
       <c r="W141" s="2">
-        <v>46.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -10462,7 +10462,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>1201.0</v>
+        <v>1417.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10471,28 +10471,28 @@
         <v>1.0</v>
       </c>
       <c r="M143" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N143" s="2">
-        <v>1200.0</v>
+        <v>1417.0</v>
       </c>
       <c r="O143" s="2">
-        <v>695.0</v>
+        <v>819.0</v>
       </c>
       <c r="P143" s="2">
-        <v>505.0</v>
+        <v>597.0</v>
       </c>
       <c r="Q143" s="2">
         <v>1.0</v>
       </c>
       <c r="R143" s="2">
-        <v>7.0</v>
+        <v>44.0</v>
       </c>
       <c r="S143" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T143" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U143" s="2">
         <v>0.0</v>
@@ -10501,7 +10501,7 @@
         <v>0.0</v>
       </c>
       <c r="W143" s="2">
-        <v>8.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
@@ -10533,7 +10533,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>1313.0</v>
+        <v>1427.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10545,34 +10545,34 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>1313.0</v>
+        <v>1427.0</v>
       </c>
       <c r="O144" s="2">
-        <v>738.0</v>
+        <v>820.0</v>
       </c>
       <c r="P144" s="2">
-        <v>575.0</v>
+        <v>607.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
       </c>
       <c r="R144" s="2">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="S144" s="2">
         <v>0.0</v>
       </c>
       <c r="T144" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="U144" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V144" s="2">
         <v>0.0</v>
       </c>
       <c r="W144" s="2">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
@@ -10675,7 +10675,7 @@
         <v>863.0</v>
       </c>
       <c r="J146" s="2">
-        <v>683.0</v>
+        <v>775.0</v>
       </c>
       <c r="K146" s="2">
         <v>1.0</v>
@@ -10687,19 +10687,19 @@
         <v>0.0</v>
       </c>
       <c r="N146" s="2">
-        <v>683.0</v>
+        <v>775.0</v>
       </c>
       <c r="O146" s="2">
-        <v>318.0</v>
+        <v>378.0</v>
       </c>
       <c r="P146" s="2">
-        <v>365.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q146" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R146" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="S146" s="2">
         <v>45.0</v>
@@ -10711,10 +10711,10 @@
         <v>3.0</v>
       </c>
       <c r="V146" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W146" s="2">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
@@ -10746,7 +10746,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>751.0</v>
+        <v>1047.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10758,16 +10758,16 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>751.0</v>
+        <v>1047.0</v>
       </c>
       <c r="O147" s="2">
-        <v>387.0</v>
+        <v>532.0</v>
       </c>
       <c r="P147" s="2">
-        <v>360.0</v>
+        <v>510.0</v>
       </c>
       <c r="Q147" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R147" s="2">
         <v>5.0</v>
@@ -10817,7 +10817,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>1100.0</v>
+        <v>1213.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10829,25 +10829,25 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>1100.0</v>
+        <v>1213.0</v>
       </c>
       <c r="O148" s="2">
-        <v>572.0</v>
+        <v>627.0</v>
       </c>
       <c r="P148" s="2">
-        <v>519.0</v>
+        <v>568.0</v>
       </c>
       <c r="Q148" s="2">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
       <c r="R148" s="2">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="S148" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="T148" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U148" s="2">
         <v>3.0</v>
@@ -10856,7 +10856,7 @@
         <v>0.0</v>
       </c>
       <c r="W148" s="2">
-        <v>34.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
@@ -10888,7 +10888,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>904.0</v>
+        <v>1087.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10900,34 +10900,34 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>904.0</v>
+        <v>1087.0</v>
       </c>
       <c r="O149" s="2">
-        <v>545.0</v>
+        <v>651.0</v>
       </c>
       <c r="P149" s="2">
-        <v>351.0</v>
+        <v>412.0</v>
       </c>
       <c r="Q149" s="2">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
       <c r="R149" s="2">
-        <v>27.0</v>
+        <v>57.0</v>
       </c>
       <c r="S149" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T149" s="2">
         <v>0.0</v>
       </c>
       <c r="U149" s="2">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="V149" s="2">
         <v>0.0</v>
       </c>
       <c r="W149" s="2">
-        <v>28.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
@@ -11030,7 +11030,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>637.0</v>
+        <v>672.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11042,25 +11042,25 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>637.0</v>
+        <v>672.0</v>
       </c>
       <c r="O151" s="2">
-        <v>334.0</v>
+        <v>364.0</v>
       </c>
       <c r="P151" s="2">
-        <v>302.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q151" s="2">
         <v>1.0</v>
       </c>
       <c r="R151" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S151" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T151" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U151" s="2">
         <v>0.0</v>
@@ -11069,7 +11069,7 @@
         <v>0.0</v>
       </c>
       <c r="W151" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
@@ -11172,7 +11172,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>876.0</v>
+        <v>957.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11184,25 +11184,25 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>876.0</v>
+        <v>957.0</v>
       </c>
       <c r="O153" s="2">
-        <v>435.0</v>
+        <v>495.0</v>
       </c>
       <c r="P153" s="2">
-        <v>440.0</v>
+        <v>457.0</v>
       </c>
       <c r="Q153" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="R153" s="2">
         <v>43.0</v>
       </c>
       <c r="S153" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="T153" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U153" s="2">
         <v>0.0</v>
@@ -11211,7 +11211,7 @@
         <v>1.0</v>
       </c>
       <c r="W153" s="2">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
@@ -11243,7 +11243,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>847.0</v>
+        <v>903.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11255,34 +11255,34 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>847.0</v>
+        <v>903.0</v>
       </c>
       <c r="O154" s="2">
-        <v>255.0</v>
+        <v>284.0</v>
       </c>
       <c r="P154" s="2">
-        <v>359.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q154" s="2">
-        <v>233.0</v>
+        <v>247.0</v>
       </c>
       <c r="R154" s="2">
-        <v>15.0</v>
+        <v>56.0</v>
       </c>
       <c r="S154" s="2">
-        <v>3.0</v>
+        <v>35.0</v>
       </c>
       <c r="T154" s="2">
         <v>0.0</v>
       </c>
       <c r="U154" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="V154" s="2">
         <v>0.0</v>
       </c>
       <c r="W154" s="2">
-        <v>19.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
@@ -11314,7 +11314,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" s="2">
-        <v>1137.0</v>
+        <v>1139.0</v>
       </c>
       <c r="K155" s="2">
         <v>1.0</v>
@@ -11326,13 +11326,13 @@
         <v>0.0</v>
       </c>
       <c r="N155" s="2">
-        <v>1137.0</v>
+        <v>1139.0</v>
       </c>
       <c r="O155" s="2">
         <v>606.0</v>
       </c>
       <c r="P155" s="2">
-        <v>530.0</v>
+        <v>532.0</v>
       </c>
       <c r="Q155" s="2">
         <v>1.0</v>
@@ -11341,7 +11341,7 @@
         <v>30.0</v>
       </c>
       <c r="S155" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="T155" s="2">
         <v>8.0</v>
@@ -11353,7 +11353,7 @@
         <v>0.0</v>
       </c>
       <c r="W155" s="2">
-        <v>43.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
@@ -11385,7 +11385,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" s="2">
-        <v>974.0</v>
+        <v>1067.0</v>
       </c>
       <c r="K156" s="2">
         <v>1.0</v>
@@ -11397,25 +11397,25 @@
         <v>0.0</v>
       </c>
       <c r="N156" s="2">
-        <v>974.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O156" s="2">
-        <v>482.0</v>
+        <v>544.0</v>
       </c>
       <c r="P156" s="2">
-        <v>491.0</v>
+        <v>520.0</v>
       </c>
       <c r="Q156" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R156" s="2">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
       <c r="S156" s="2">
         <v>1.0</v>
       </c>
       <c r="T156" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U156" s="2">
         <v>0.0</v>
@@ -11424,7 +11424,7 @@
         <v>0.0</v>
       </c>
       <c r="W156" s="2">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
@@ -11456,7 +11456,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" s="2">
-        <v>1208.0</v>
+        <v>1288.0</v>
       </c>
       <c r="K157" s="2">
         <v>1.0</v>
@@ -11468,19 +11468,19 @@
         <v>4.0</v>
       </c>
       <c r="N157" s="2">
-        <v>1204.0</v>
+        <v>1284.0</v>
       </c>
       <c r="O157" s="2">
-        <v>622.0</v>
+        <v>654.0</v>
       </c>
       <c r="P157" s="2">
-        <v>586.0</v>
+        <v>605.0</v>
       </c>
       <c r="Q157" s="2">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="R157" s="2">
-        <v>21.0</v>
+        <v>100.0</v>
       </c>
       <c r="S157" s="2">
         <v>0.0</v>
@@ -11495,7 +11495,7 @@
         <v>0.0</v>
       </c>
       <c r="W157" s="2">
-        <v>23.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
@@ -11527,7 +11527,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>1120.0</v>
+        <v>1241.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11539,34 +11539,34 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>1120.0</v>
+        <v>1241.0</v>
       </c>
       <c r="O158" s="2">
-        <v>525.0</v>
+        <v>591.0</v>
       </c>
       <c r="P158" s="2">
-        <v>595.0</v>
+        <v>650.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
       </c>
       <c r="R158" s="2">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
       <c r="S158" s="2">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
       <c r="T158" s="2">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="U158" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="V158" s="2">
         <v>0.0</v>
       </c>
       <c r="W158" s="2">
-        <v>81.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
@@ -11598,7 +11598,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>1068.0</v>
+        <v>1077.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11607,16 +11607,16 @@
         <v>1.0</v>
       </c>
       <c r="M159" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N159" s="2">
-        <v>1067.0</v>
+        <v>1077.0</v>
       </c>
       <c r="O159" s="2">
-        <v>625.0</v>
+        <v>633.0</v>
       </c>
       <c r="P159" s="2">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11625,19 +11625,19 @@
         <v>32.0</v>
       </c>
       <c r="S159" s="2">
-        <v>15.0</v>
+        <v>24.0</v>
       </c>
       <c r="T159" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="U159" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="V159" s="2">
         <v>0.0</v>
       </c>
       <c r="W159" s="2">
-        <v>53.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
@@ -11669,7 +11669,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>1207.0</v>
+        <v>1261.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11681,34 +11681,34 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>1207.0</v>
+        <v>1261.0</v>
       </c>
       <c r="O160" s="2">
-        <v>613.0</v>
+        <v>630.0</v>
       </c>
       <c r="P160" s="2">
-        <v>594.0</v>
+        <v>631.0</v>
       </c>
       <c r="Q160" s="2">
         <v>0.0</v>
       </c>
       <c r="R160" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S160" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="T160" s="2">
         <v>2.0</v>
       </c>
-      <c r="S160" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="T160" s="2">
-        <v>1.0</v>
-      </c>
       <c r="U160" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V160" s="2">
         <v>0.0</v>
       </c>
       <c r="W160" s="2">
-        <v>3.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
@@ -11740,7 +11740,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>1132.0</v>
+        <v>1306.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11752,22 +11752,22 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>1132.0</v>
+        <v>1306.0</v>
       </c>
       <c r="O161" s="2">
-        <v>614.0</v>
+        <v>723.0</v>
       </c>
       <c r="P161" s="2">
-        <v>500.0</v>
+        <v>560.0</v>
       </c>
       <c r="Q161" s="2">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="R161" s="2">
-        <v>21.0</v>
+        <v>25.0</v>
       </c>
       <c r="S161" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="T161" s="2">
         <v>0.0</v>
@@ -11779,7 +11779,7 @@
         <v>0.0</v>
       </c>
       <c r="W161" s="2">
-        <v>44.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
@@ -11811,7 +11811,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>1117.0</v>
+        <v>1143.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11820,28 +11820,28 @@
         <v>1.0</v>
       </c>
       <c r="M162" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N162" s="2">
-        <v>1116.0</v>
+        <v>1143.0</v>
       </c>
       <c r="O162" s="2">
-        <v>111.0</v>
+        <v>118.0</v>
       </c>
       <c r="P162" s="2">
-        <v>266.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>740.0</v>
+        <v>755.0</v>
       </c>
       <c r="R162" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="S162" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T162" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="U162" s="2">
         <v>0.0</v>
@@ -11850,7 +11850,7 @@
         <v>1.0</v>
       </c>
       <c r="W162" s="2">
-        <v>31.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
@@ -11882,7 +11882,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>983.0</v>
+        <v>1112.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11894,25 +11894,25 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>983.0</v>
+        <v>1112.0</v>
       </c>
       <c r="O163" s="2">
-        <v>99.0</v>
+        <v>111.0</v>
       </c>
       <c r="P163" s="2">
-        <v>483.0</v>
+        <v>541.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>401.0</v>
+        <v>460.0</v>
       </c>
       <c r="R163" s="2">
-        <v>89.0</v>
+        <v>103.0</v>
       </c>
       <c r="S163" s="2">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
       <c r="T163" s="2">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="U163" s="2">
         <v>5.0</v>
@@ -11921,7 +11921,7 @@
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>163.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -12237,7 +12237,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>920.0</v>
+        <v>924.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12249,16 +12249,16 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>920.0</v>
+        <v>924.0</v>
       </c>
       <c r="O168" s="2">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
       <c r="P168" s="2">
         <v>415.0</v>
       </c>
       <c r="Q168" s="2">
-        <v>139.0</v>
+        <v>142.0</v>
       </c>
       <c r="R168" s="2">
         <v>22.0</v>
@@ -12323,13 +12323,13 @@
         <v>471.0</v>
       </c>
       <c r="O169" s="2">
-        <v>247.0</v>
+        <v>255.0</v>
       </c>
       <c r="P169" s="2">
         <v>215.0</v>
       </c>
       <c r="Q169" s="2">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="R169" s="2">
         <v>11.0</v>
@@ -12379,7 +12379,7 @@
         <v>968.0</v>
       </c>
       <c r="J170" s="2">
-        <v>866.0</v>
+        <v>869.0</v>
       </c>
       <c r="K170" s="2">
         <v>1.0</v>
@@ -12391,10 +12391,10 @@
         <v>0.0</v>
       </c>
       <c r="N170" s="2">
-        <v>866.0</v>
+        <v>869.0</v>
       </c>
       <c r="O170" s="2">
-        <v>142.0</v>
+        <v>145.0</v>
       </c>
       <c r="P170" s="2">
         <v>394.0</v>
@@ -12412,13 +12412,13 @@
         <v>8.0</v>
       </c>
       <c r="U170" s="2">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="V170" s="2">
         <v>0.0</v>
       </c>
       <c r="W170" s="2">
-        <v>95.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
@@ -12521,7 +12521,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" s="2">
-        <v>891.0</v>
+        <v>924.0</v>
       </c>
       <c r="K172" s="2">
         <v>1.0</v>
@@ -12533,22 +12533,22 @@
         <v>0.0</v>
       </c>
       <c r="N172" s="2">
-        <v>891.0</v>
+        <v>924.0</v>
       </c>
       <c r="O172" s="2">
-        <v>507.0</v>
+        <v>528.0</v>
       </c>
       <c r="P172" s="2">
-        <v>384.0</v>
+        <v>396.0</v>
       </c>
       <c r="Q172" s="2">
         <v>0.0</v>
       </c>
       <c r="R172" s="2">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="S172" s="2">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
       <c r="T172" s="2">
         <v>14.0</v>
@@ -12560,7 +12560,7 @@
         <v>0.0</v>
       </c>
       <c r="W172" s="2">
-        <v>151.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
@@ -12592,7 +12592,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" s="2">
-        <v>1142.0</v>
+        <v>1206.0</v>
       </c>
       <c r="K173" s="2">
         <v>1.0</v>
@@ -12604,34 +12604,34 @@
         <v>0.0</v>
       </c>
       <c r="N173" s="2">
-        <v>1142.0</v>
+        <v>1206.0</v>
       </c>
       <c r="O173" s="2">
-        <v>650.0</v>
+        <v>669.0</v>
       </c>
       <c r="P173" s="2">
-        <v>492.0</v>
+        <v>537.0</v>
       </c>
       <c r="Q173" s="2">
         <v>0.0</v>
       </c>
       <c r="R173" s="2">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
       <c r="S173" s="2">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="T173" s="2">
         <v>2.0</v>
       </c>
       <c r="U173" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V173" s="2">
         <v>0.0</v>
       </c>
       <c r="W173" s="2">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
@@ -12663,7 +12663,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" s="2">
-        <v>1085.0</v>
+        <v>1215.0</v>
       </c>
       <c r="K174" s="2">
         <v>1.0</v>
@@ -12675,22 +12675,22 @@
         <v>0.0</v>
       </c>
       <c r="N174" s="2">
-        <v>1085.0</v>
+        <v>1215.0</v>
       </c>
       <c r="O174" s="2">
-        <v>546.0</v>
+        <v>625.0</v>
       </c>
       <c r="P174" s="2">
-        <v>539.0</v>
+        <v>590.0</v>
       </c>
       <c r="Q174" s="2">
         <v>0.0</v>
       </c>
       <c r="R174" s="2">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="S174" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="T174" s="2">
         <v>0.0</v>
@@ -12702,7 +12702,7 @@
         <v>0.0</v>
       </c>
       <c r="W174" s="2">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
@@ -12749,10 +12749,10 @@
         <v>1149.0</v>
       </c>
       <c r="O175" s="2">
-        <v>522.0</v>
+        <v>524.0</v>
       </c>
       <c r="P175" s="2">
-        <v>627.0</v>
+        <v>625.0</v>
       </c>
       <c r="Q175" s="2">
         <v>0.0</v>
@@ -12805,7 +12805,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>868.0</v>
+        <v>896.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12817,34 +12817,34 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>868.0</v>
+        <v>896.0</v>
       </c>
       <c r="O176" s="2">
-        <v>419.0</v>
+        <v>439.0</v>
       </c>
       <c r="P176" s="2">
-        <v>445.0</v>
+        <v>452.0</v>
       </c>
       <c r="Q176" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R176" s="2">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="S176" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="T176" s="2">
         <v>1.0</v>
       </c>
       <c r="U176" s="2">
-        <v>46.0</v>
+        <v>52.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>141.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12876,7 +12876,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>849.0</v>
+        <v>929.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12888,34 +12888,34 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>849.0</v>
+        <v>929.0</v>
       </c>
       <c r="O177" s="2">
-        <v>500.0</v>
+        <v>550.0</v>
       </c>
       <c r="P177" s="2">
-        <v>349.0</v>
+        <v>379.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
       </c>
       <c r="R177" s="2">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
       <c r="S177" s="2">
-        <v>42.0</v>
+        <v>55.0</v>
       </c>
       <c r="T177" s="2">
         <v>5.0</v>
       </c>
       <c r="U177" s="2">
-        <v>30.0</v>
+        <v>45.0</v>
       </c>
       <c r="V177" s="2">
         <v>0.0</v>
       </c>
       <c r="W177" s="2">
-        <v>103.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
@@ -12947,7 +12947,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>747.0</v>
+        <v>795.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12959,34 +12959,34 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>747.0</v>
+        <v>795.0</v>
       </c>
       <c r="O178" s="2">
-        <v>373.0</v>
+        <v>399.0</v>
       </c>
       <c r="P178" s="2">
-        <v>373.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
       </c>
       <c r="R178" s="2">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="S178" s="2">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="T178" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="U178" s="2">
-        <v>93.0</v>
+        <v>134.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>129.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13018,7 +13018,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>945.0</v>
+        <v>974.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13030,19 +13030,19 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>945.0</v>
+        <v>974.0</v>
       </c>
       <c r="O179" s="2">
-        <v>583.0</v>
+        <v>595.0</v>
       </c>
       <c r="P179" s="2">
-        <v>361.0</v>
+        <v>378.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="S179" s="2">
         <v>14.0</v>
@@ -13051,13 +13051,13 @@
         <v>0.0</v>
       </c>
       <c r="U179" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="V179" s="2">
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>82.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13089,7 +13089,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>662.0</v>
+        <v>705.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13101,22 +13101,22 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>662.0</v>
+        <v>705.0</v>
       </c>
       <c r="O180" s="2">
-        <v>353.0</v>
+        <v>373.0</v>
       </c>
       <c r="P180" s="2">
-        <v>309.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
       </c>
       <c r="R180" s="2">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="S180" s="2">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
       <c r="T180" s="2">
         <v>3.0</v>
@@ -13128,7 +13128,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" s="2">
-        <v>66.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -13160,7 +13160,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" s="2">
-        <v>625.0</v>
+        <v>643.0</v>
       </c>
       <c r="K181" s="2">
         <v>1.0</v>
@@ -13172,34 +13172,34 @@
         <v>0.0</v>
       </c>
       <c r="N181" s="2">
-        <v>625.0</v>
+        <v>643.0</v>
       </c>
       <c r="O181" s="2">
-        <v>337.0</v>
+        <v>350.0</v>
       </c>
       <c r="P181" s="2">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="Q181" s="2">
         <v>0.0</v>
       </c>
       <c r="R181" s="2">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="S181" s="2">
-        <v>45.0</v>
+        <v>62.0</v>
       </c>
       <c r="T181" s="2">
         <v>2.0</v>
       </c>
       <c r="U181" s="2">
-        <v>110.0</v>
+        <v>128.0</v>
       </c>
       <c r="V181" s="2">
         <v>0.0</v>
       </c>
       <c r="W181" s="2">
-        <v>172.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -13373,7 +13373,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
-        <v>701.0</v>
+        <v>759.0</v>
       </c>
       <c r="K184" s="2">
         <v>1.0</v>
@@ -13385,34 +13385,34 @@
         <v>1.0</v>
       </c>
       <c r="N184" s="2">
-        <v>700.0</v>
+        <v>758.0</v>
       </c>
       <c r="O184" s="2">
-        <v>349.0</v>
+        <v>375.0</v>
       </c>
       <c r="P184" s="2">
-        <v>351.0</v>
+        <v>382.0</v>
       </c>
       <c r="Q184" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R184" s="2">
-        <v>21.0</v>
+        <v>35.0</v>
       </c>
       <c r="S184" s="2">
-        <v>28.0</v>
+        <v>62.0</v>
       </c>
       <c r="T184" s="2">
         <v>4.0</v>
       </c>
       <c r="U184" s="2">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
       <c r="V184" s="2">
         <v>0.0</v>
       </c>
       <c r="W184" s="2">
-        <v>87.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
@@ -13444,7 +13444,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>950.0</v>
+        <v>959.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13456,22 +13456,22 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>950.0</v>
+        <v>959.0</v>
       </c>
       <c r="O185" s="2">
-        <v>514.0</v>
+        <v>517.0</v>
       </c>
       <c r="P185" s="2">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
       <c r="Q185" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R185" s="2">
         <v>19.0</v>
       </c>
       <c r="S185" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="T185" s="2">
         <v>1.0</v>
@@ -13483,7 +13483,7 @@
         <v>0.0</v>
       </c>
       <c r="W185" s="2">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
@@ -13586,7 +13586,7 @@
         <v>990.0</v>
       </c>
       <c r="J187" s="2">
-        <v>832.0</v>
+        <v>861.0</v>
       </c>
       <c r="K187" s="2">
         <v>1.0</v>
@@ -13598,13 +13598,13 @@
         <v>0.0</v>
       </c>
       <c r="N187" s="2">
-        <v>832.0</v>
+        <v>861.0</v>
       </c>
       <c r="O187" s="2">
-        <v>498.0</v>
+        <v>500.0</v>
       </c>
       <c r="P187" s="2">
-        <v>334.0</v>
+        <v>361.0</v>
       </c>
       <c r="Q187" s="2">
         <v>0.0</v>
@@ -13613,19 +13613,19 @@
         <v>40.0</v>
       </c>
       <c r="S187" s="2">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="T187" s="2">
         <v>0.0</v>
       </c>
       <c r="U187" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V187" s="2">
         <v>1.0</v>
       </c>
       <c r="W187" s="2">
-        <v>125.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
@@ -13657,7 +13657,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>893.0</v>
+        <v>911.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13669,22 +13669,22 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>893.0</v>
+        <v>911.0</v>
       </c>
       <c r="O188" s="2">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="P188" s="2">
-        <v>395.0</v>
+        <v>410.0</v>
       </c>
       <c r="Q188" s="2">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
       <c r="R188" s="2">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="S188" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="T188" s="2">
         <v>1.0</v>
@@ -13696,7 +13696,7 @@
         <v>0.0</v>
       </c>
       <c r="W188" s="2">
-        <v>103.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
@@ -13728,7 +13728,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>1208.0</v>
+        <v>1220.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13740,22 +13740,22 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>1208.0</v>
+        <v>1220.0</v>
       </c>
       <c r="O189" s="2">
-        <v>505.0</v>
+        <v>514.0</v>
       </c>
       <c r="P189" s="2">
-        <v>422.0</v>
+        <v>424.0</v>
       </c>
       <c r="Q189" s="2">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="R189" s="2">
         <v>40.0</v>
       </c>
       <c r="S189" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T189" s="2">
         <v>6.0</v>
@@ -13767,7 +13767,7 @@
         <v>0.0</v>
       </c>
       <c r="W189" s="2">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
@@ -13799,7 +13799,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>1256.0</v>
+        <v>1262.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13811,16 +13811,16 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>1256.0</v>
+        <v>1262.0</v>
       </c>
       <c r="O190" s="2">
-        <v>743.0</v>
+        <v>744.0</v>
       </c>
       <c r="P190" s="2">
         <v>481.0</v>
       </c>
       <c r="Q190" s="2">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
       <c r="R190" s="2">
         <v>55.0</v>
@@ -13870,7 +13870,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>1249.0</v>
+        <v>1299.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13882,16 +13882,16 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>1249.0</v>
+        <v>1299.0</v>
       </c>
       <c r="O191" s="2">
-        <v>728.0</v>
+        <v>772.0</v>
       </c>
       <c r="P191" s="2">
-        <v>480.0</v>
+        <v>492.0</v>
       </c>
       <c r="Q191" s="2">
-        <v>41.0</v>
+        <v>35.0</v>
       </c>
       <c r="R191" s="2">
         <v>47.0</v>
@@ -13941,7 +13941,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>465.0</v>
+        <v>470.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13953,10 +13953,10 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>465.0</v>
+        <v>470.0</v>
       </c>
       <c r="O192" s="2">
-        <v>289.0</v>
+        <v>294.0</v>
       </c>
       <c r="P192" s="2">
         <v>171.0</v>
@@ -13971,7 +13971,7 @@
         <v>5.0</v>
       </c>
       <c r="T192" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U192" s="2">
         <v>1.0</v>
@@ -13980,7 +13980,7 @@
         <v>0.0</v>
       </c>
       <c r="W192" s="2">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -14012,7 +14012,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>1256.0</v>
+        <v>1284.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14024,25 +14024,25 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>1256.0</v>
+        <v>1284.0</v>
       </c>
       <c r="O193" s="2">
-        <v>477.0</v>
+        <v>491.0</v>
       </c>
       <c r="P193" s="2">
-        <v>556.0</v>
+        <v>565.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>223.0</v>
+        <v>228.0</v>
       </c>
       <c r="R193" s="2">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="S193" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="T193" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U193" s="2">
         <v>0.0</v>
@@ -14051,7 +14051,7 @@
         <v>0.0</v>
       </c>
       <c r="W193" s="2">
-        <v>29.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
@@ -14098,13 +14098,13 @@
         <v>435.0</v>
       </c>
       <c r="O194" s="2">
-        <v>160.0</v>
+        <v>189.0</v>
       </c>
       <c r="P194" s="2">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="Q194" s="2">
-        <v>36.0</v>
+        <v>6.0</v>
       </c>
       <c r="R194" s="2">
         <v>13.0</v>
@@ -14169,13 +14169,13 @@
         <v>538.0</v>
       </c>
       <c r="O195" s="2">
-        <v>198.0</v>
+        <v>234.0</v>
       </c>
       <c r="P195" s="2">
         <v>212.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>128.0</v>
+        <v>92.0</v>
       </c>
       <c r="R195" s="2">
         <v>13.0</v>
@@ -14240,13 +14240,13 @@
         <v>1307.0</v>
       </c>
       <c r="O196" s="2">
-        <v>563.0</v>
+        <v>569.0</v>
       </c>
       <c r="P196" s="2">
-        <v>546.0</v>
+        <v>545.0</v>
       </c>
       <c r="Q196" s="2">
-        <v>198.0</v>
+        <v>193.0</v>
       </c>
       <c r="R196" s="2">
         <v>38.0</v>
@@ -14311,13 +14311,13 @@
         <v>1083.0</v>
       </c>
       <c r="O197" s="2">
-        <v>612.0</v>
+        <v>686.0</v>
       </c>
       <c r="P197" s="2">
-        <v>353.0</v>
+        <v>357.0</v>
       </c>
       <c r="Q197" s="2">
-        <v>118.0</v>
+        <v>40.0</v>
       </c>
       <c r="R197" s="2">
         <v>29.0</v>
@@ -14382,13 +14382,13 @@
         <v>1291.0</v>
       </c>
       <c r="O198" s="2">
-        <v>384.0</v>
+        <v>503.0</v>
       </c>
       <c r="P198" s="2">
-        <v>631.0</v>
+        <v>638.0</v>
       </c>
       <c r="Q198" s="2">
-        <v>276.0</v>
+        <v>150.0</v>
       </c>
       <c r="R198" s="2">
         <v>52.0</v>
@@ -14536,7 +14536,7 @@
         <v>23.0</v>
       </c>
       <c r="S200" s="2">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="T200" s="2">
         <v>2.0</v>
@@ -14548,7 +14548,7 @@
         <v>4.0</v>
       </c>
       <c r="W200" s="2">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -14580,7 +14580,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>1197.0</v>
+        <v>1207.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14592,19 +14592,19 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>1197.0</v>
+        <v>1207.0</v>
       </c>
       <c r="O201" s="2">
-        <v>635.0</v>
+        <v>640.0</v>
       </c>
       <c r="P201" s="2">
-        <v>550.0</v>
+        <v>555.0</v>
       </c>
       <c r="Q201" s="2">
         <v>12.0</v>
       </c>
       <c r="R201" s="2">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="S201" s="2">
         <v>26.0</v>
@@ -14619,7 +14619,7 @@
         <v>1.0</v>
       </c>
       <c r="W201" s="2">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
@@ -14651,7 +14651,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>1075.0</v>
+        <v>1100.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14663,19 +14663,19 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>1075.0</v>
+        <v>1100.0</v>
       </c>
       <c r="O202" s="2">
-        <v>652.0</v>
+        <v>668.0</v>
       </c>
       <c r="P202" s="2">
-        <v>423.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
       </c>
       <c r="R202" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="S202" s="2">
         <v>30.0</v>
@@ -14690,7 +14690,7 @@
         <v>1.0</v>
       </c>
       <c r="W202" s="2">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
@@ -14722,7 +14722,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>1032.0</v>
+        <v>1099.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14734,34 +14734,34 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>1032.0</v>
+        <v>1099.0</v>
       </c>
       <c r="O203" s="2">
-        <v>618.0</v>
+        <v>655.0</v>
       </c>
       <c r="P203" s="2">
-        <v>409.0</v>
+        <v>440.0</v>
       </c>
       <c r="Q203" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R203" s="2">
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="S203" s="2">
-        <v>59.0</v>
+        <v>64.0</v>
       </c>
       <c r="T203" s="2">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="U203" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V203" s="2">
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>142.0</v>
+        <v>158.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14793,7 +14793,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>1061.0</v>
+        <v>1141.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14805,19 +14805,19 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>1061.0</v>
+        <v>1141.0</v>
       </c>
       <c r="O204" s="2">
-        <v>569.0</v>
+        <v>618.0</v>
       </c>
       <c r="P204" s="2">
-        <v>474.0</v>
+        <v>498.0</v>
       </c>
       <c r="Q204" s="2">
-        <v>18.0</v>
+        <v>25.0</v>
       </c>
       <c r="R204" s="2">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
       <c r="S204" s="2">
         <v>15.0</v>
@@ -14826,13 +14826,13 @@
         <v>0.0</v>
       </c>
       <c r="U204" s="2">
-        <v>33.0</v>
+        <v>41.0</v>
       </c>
       <c r="V204" s="2">
         <v>0.0</v>
       </c>
       <c r="W204" s="2">
-        <v>82.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
@@ -14864,7 +14864,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>813.0</v>
+        <v>817.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14876,34 +14876,34 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>813.0</v>
+        <v>817.0</v>
       </c>
       <c r="O205" s="2">
-        <v>443.0</v>
+        <v>446.0</v>
       </c>
       <c r="P205" s="2">
         <v>320.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="R205" s="2">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="S205" s="2">
         <v>26.0</v>
       </c>
       <c r="T205" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U205" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="V205" s="2">
         <v>0.0</v>
       </c>
       <c r="W205" s="2">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1">
@@ -14935,7 +14935,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>810.0</v>
+        <v>814.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14947,13 +14947,13 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>810.0</v>
+        <v>814.0</v>
       </c>
       <c r="O206" s="2">
-        <v>521.0</v>
+        <v>524.0</v>
       </c>
       <c r="P206" s="2">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="Q206" s="2">
         <v>0.0</v>
@@ -15006,7 +15006,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>845.0</v>
+        <v>864.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15018,13 +15018,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>845.0</v>
+        <v>864.0</v>
       </c>
       <c r="O207" s="2">
-        <v>457.0</v>
+        <v>464.0</v>
       </c>
       <c r="P207" s="2">
-        <v>374.0</v>
+        <v>386.0</v>
       </c>
       <c r="Q207" s="2">
         <v>14.0</v>
@@ -15092,13 +15092,13 @@
         <v>663.0</v>
       </c>
       <c r="O208" s="2">
-        <v>225.0</v>
+        <v>224.0</v>
       </c>
       <c r="P208" s="2">
         <v>272.0</v>
       </c>
       <c r="Q208" s="2">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="R208" s="2">
         <v>8.0</v>
@@ -15148,7 +15148,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>840.0</v>
+        <v>841.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15160,10 +15160,10 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>840.0</v>
+        <v>841.0</v>
       </c>
       <c r="O209" s="2">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
       <c r="P209" s="2">
         <v>404.0</v>
@@ -15175,7 +15175,7 @@
         <v>47.0</v>
       </c>
       <c r="S209" s="2">
-        <v>57.0</v>
+        <v>56.0</v>
       </c>
       <c r="T209" s="2">
         <v>6.0</v>
@@ -15187,7 +15187,7 @@
         <v>1.0</v>
       </c>
       <c r="W209" s="2">
-        <v>111.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
@@ -15432,7 +15432,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>858.0</v>
+        <v>864.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15444,13 +15444,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>858.0</v>
+        <v>864.0</v>
       </c>
       <c r="O213" s="2">
-        <v>494.0</v>
+        <v>497.0</v>
       </c>
       <c r="P213" s="2">
-        <v>364.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15459,19 +15459,19 @@
         <v>43.0</v>
       </c>
       <c r="S213" s="2">
-        <v>39.0</v>
+        <v>59.0</v>
       </c>
       <c r="T213" s="2">
         <v>0.0</v>
       </c>
       <c r="U213" s="2">
-        <v>3.0</v>
+        <v>67.0</v>
       </c>
       <c r="V213" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W213" s="2">
-        <v>85.0</v>
+        <v>170.0</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
@@ -15503,7 +15503,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>871.0</v>
+        <v>879.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -15515,13 +15515,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>871.0</v>
+        <v>879.0</v>
       </c>
       <c r="O214" s="2">
-        <v>467.0</v>
+        <v>471.0</v>
       </c>
       <c r="P214" s="2">
-        <v>404.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
@@ -15530,19 +15530,19 @@
         <v>30.0</v>
       </c>
       <c r="S214" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T214" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="U214" s="2">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
       <c r="V214" s="2">
         <v>5.0</v>
       </c>
       <c r="W214" s="2">
-        <v>130.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
@@ -15589,19 +15589,19 @@
         <v>1002.0</v>
       </c>
       <c r="O215" s="2">
-        <v>506.0</v>
+        <v>507.0</v>
       </c>
       <c r="P215" s="2">
         <v>473.0</v>
       </c>
       <c r="Q215" s="2">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="R215" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="S215" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="T215" s="2">
         <v>7.0</v>
@@ -15645,7 +15645,7 @@
         <v>576.0</v>
       </c>
       <c r="J216" s="2">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="K216" s="2">
         <v>1.0</v>
@@ -15657,7 +15657,7 @@
         <v>0.0</v>
       </c>
       <c r="N216" s="2">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="O216" s="2">
         <v>273.0</v>
@@ -15666,7 +15666,7 @@
         <v>237.0</v>
       </c>
       <c r="Q216" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R216" s="2">
         <v>23.0</v>
@@ -15716,7 +15716,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>901.0</v>
+        <v>1004.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15728,34 +15728,34 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>901.0</v>
+        <v>1004.0</v>
       </c>
       <c r="O217" s="2">
-        <v>468.0</v>
+        <v>509.0</v>
       </c>
       <c r="P217" s="2">
-        <v>432.0</v>
+        <v>479.0</v>
       </c>
       <c r="Q217" s="2">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="R217" s="2">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
       <c r="S217" s="2">
-        <v>51.0</v>
+        <v>57.0</v>
       </c>
       <c r="T217" s="2">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="U217" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="V217" s="2">
         <v>0.0</v>
       </c>
       <c r="W217" s="2">
-        <v>107.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
@@ -15787,7 +15787,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>983.0</v>
+        <v>1059.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15799,34 +15799,34 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>982.0</v>
+        <v>1058.0</v>
       </c>
       <c r="O218" s="2">
-        <v>498.0</v>
+        <v>544.0</v>
       </c>
       <c r="P218" s="2">
-        <v>485.0</v>
+        <v>515.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>52.0</v>
+        <v>61.0</v>
       </c>
       <c r="S218" s="2">
-        <v>35.0</v>
+        <v>43.0</v>
       </c>
       <c r="T218" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="U218" s="2">
-        <v>7.0</v>
+        <v>17.0</v>
       </c>
       <c r="V218" s="2">
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>103.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15858,7 +15858,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>1201.0</v>
+        <v>1296.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15870,25 +15870,25 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>1201.0</v>
+        <v>1296.0</v>
       </c>
       <c r="O219" s="2">
-        <v>307.0</v>
+        <v>358.0</v>
       </c>
       <c r="P219" s="2">
-        <v>511.0</v>
+        <v>551.0</v>
       </c>
       <c r="Q219" s="2">
-        <v>383.0</v>
+        <v>387.0</v>
       </c>
       <c r="R219" s="2">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="S219" s="2">
-        <v>62.0</v>
+        <v>73.0</v>
       </c>
       <c r="T219" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U219" s="2">
         <v>1.0</v>
@@ -15897,7 +15897,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>96.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -15944,13 +15944,13 @@
         <v>767.0</v>
       </c>
       <c r="O220" s="2">
-        <v>188.0</v>
+        <v>204.0</v>
       </c>
       <c r="P220" s="2">
-        <v>344.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q220" s="2">
-        <v>235.0</v>
+        <v>220.0</v>
       </c>
       <c r="R220" s="2">
         <v>16.0</v>
@@ -16000,7 +16000,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" s="2">
-        <v>821.0</v>
+        <v>823.0</v>
       </c>
       <c r="K221" s="2">
         <v>1.0</v>
@@ -16009,19 +16009,19 @@
         <v>1.0</v>
       </c>
       <c r="M221" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N221" s="2">
-        <v>820.0</v>
+        <v>823.0</v>
       </c>
       <c r="O221" s="2">
-        <v>254.0</v>
+        <v>259.0</v>
       </c>
       <c r="P221" s="2">
-        <v>316.0</v>
+        <v>320.0</v>
       </c>
       <c r="Q221" s="2">
-        <v>251.0</v>
+        <v>244.0</v>
       </c>
       <c r="R221" s="2">
         <v>9.0</v>
@@ -16071,7 +16071,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>1007.0</v>
+        <v>1012.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16083,22 +16083,22 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>1007.0</v>
+        <v>1012.0</v>
       </c>
       <c r="O222" s="2">
-        <v>312.0</v>
+        <v>407.0</v>
       </c>
       <c r="P222" s="2">
-        <v>442.0</v>
+        <v>459.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>253.0</v>
+        <v>146.0</v>
       </c>
       <c r="R222" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="S222" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="T222" s="2">
         <v>0.0</v>
@@ -16110,7 +16110,7 @@
         <v>0.0</v>
       </c>
       <c r="W222" s="2">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
@@ -16142,7 +16142,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>1025.0</v>
+        <v>1127.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16154,25 +16154,25 @@
         <v>2.0</v>
       </c>
       <c r="N223" s="2">
-        <v>1023.0</v>
+        <v>1125.0</v>
       </c>
       <c r="O223" s="2">
-        <v>115.0</v>
+        <v>169.0</v>
       </c>
       <c r="P223" s="2">
-        <v>287.0</v>
+        <v>317.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>623.0</v>
+        <v>641.0</v>
       </c>
       <c r="R223" s="2">
-        <v>73.0</v>
+        <v>78.0</v>
       </c>
       <c r="S223" s="2">
-        <v>34.0</v>
+        <v>40.0</v>
       </c>
       <c r="T223" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="U223" s="2">
         <v>0.0</v>
@@ -16181,7 +16181,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>118.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16237,22 +16237,22 @@
         <v>638.0</v>
       </c>
       <c r="R224" s="2">
-        <v>26.0</v>
+        <v>38.0</v>
       </c>
       <c r="S224" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="T224" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="U224" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V224" s="2">
         <v>0.0</v>
       </c>
       <c r="W224" s="2">
-        <v>42.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
@@ -16284,7 +16284,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" s="2">
-        <v>1291.0</v>
+        <v>1289.0</v>
       </c>
       <c r="K225" s="2">
         <v>1.0</v>
@@ -16296,13 +16296,13 @@
         <v>0.0</v>
       </c>
       <c r="N225" s="2">
-        <v>1291.0</v>
+        <v>1289.0</v>
       </c>
       <c r="O225" s="2">
-        <v>730.0</v>
+        <v>729.0</v>
       </c>
       <c r="P225" s="2">
-        <v>553.0</v>
+        <v>552.0</v>
       </c>
       <c r="Q225" s="2">
         <v>8.0</v>
@@ -16311,10 +16311,10 @@
         <v>47.0</v>
       </c>
       <c r="S225" s="2">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="T225" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U225" s="2">
         <v>4.0</v>
@@ -16323,7 +16323,7 @@
         <v>0.0</v>
       </c>
       <c r="W225" s="2">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
@@ -16355,7 +16355,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>943.0</v>
+        <v>1060.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16367,22 +16367,22 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>943.0</v>
+        <v>1060.0</v>
       </c>
       <c r="O226" s="2">
-        <v>197.0</v>
+        <v>262.0</v>
       </c>
       <c r="P226" s="2">
-        <v>417.0</v>
+        <v>458.0</v>
       </c>
       <c r="Q226" s="2">
-        <v>329.0</v>
+        <v>340.0</v>
       </c>
       <c r="R226" s="2">
-        <v>138.0</v>
+        <v>149.0</v>
       </c>
       <c r="S226" s="2">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
       <c r="T226" s="2">
         <v>0.0</v>
@@ -16394,7 +16394,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>182.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16426,7 +16426,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" s="2">
-        <v>387.0</v>
+        <v>408.0</v>
       </c>
       <c r="K227" s="2">
         <v>1.0</v>
@@ -16438,22 +16438,22 @@
         <v>0.0</v>
       </c>
       <c r="N227" s="2">
-        <v>387.0</v>
+        <v>408.0</v>
       </c>
       <c r="O227" s="2">
-        <v>247.0</v>
+        <v>261.0</v>
       </c>
       <c r="P227" s="2">
-        <v>140.0</v>
+        <v>147.0</v>
       </c>
       <c r="Q227" s="2">
         <v>0.0</v>
       </c>
       <c r="R227" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S227" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="T227" s="2">
         <v>1.0</v>
@@ -16465,7 +16465,7 @@
         <v>0.0</v>
       </c>
       <c r="W227" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
@@ -16497,7 +16497,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>1188.0</v>
+        <v>1296.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16509,19 +16509,19 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>1188.0</v>
+        <v>1296.0</v>
       </c>
       <c r="O228" s="2">
-        <v>396.0</v>
+        <v>458.0</v>
       </c>
       <c r="P228" s="2">
-        <v>455.0</v>
+        <v>492.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>337.0</v>
+        <v>346.0</v>
       </c>
       <c r="R228" s="2">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="S228" s="2">
         <v>19.0</v>
@@ -16536,7 +16536,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16639,7 +16639,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>744.0</v>
+        <v>841.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16651,25 +16651,25 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>744.0</v>
+        <v>841.0</v>
       </c>
       <c r="O230" s="2">
-        <v>250.0</v>
+        <v>317.0</v>
       </c>
       <c r="P230" s="2">
-        <v>301.0</v>
+        <v>326.0</v>
       </c>
       <c r="Q230" s="2">
-        <v>193.0</v>
+        <v>198.0</v>
       </c>
       <c r="R230" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="S230" s="2">
         <v>18.0</v>
       </c>
-      <c r="S230" s="2">
-        <v>14.0</v>
-      </c>
       <c r="T230" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U230" s="2">
         <v>0.0</v>
@@ -16678,7 +16678,7 @@
         <v>0.0</v>
       </c>
       <c r="W230" s="2">
-        <v>32.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
@@ -16781,7 +16781,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>1065.0</v>
+        <v>1116.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16793,34 +16793,34 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>1065.0</v>
+        <v>1116.0</v>
       </c>
       <c r="O232" s="2">
-        <v>176.0</v>
+        <v>204.0</v>
       </c>
       <c r="P232" s="2">
-        <v>223.0</v>
+        <v>231.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>666.0</v>
+        <v>681.0</v>
       </c>
       <c r="R232" s="2">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="S232" s="2">
-        <v>89.0</v>
+        <v>106.0</v>
       </c>
       <c r="T232" s="2">
         <v>0.0</v>
       </c>
       <c r="U232" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="V232" s="2">
         <v>0.0</v>
       </c>
       <c r="W232" s="2">
-        <v>146.0</v>
+        <v>171.0</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
